--- a/paper/data/merapi_cpx.xlsx
+++ b/paper/data/merapi_cpx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13493\Documents\PROJECTS\Cpx_thermobarometry_recommend_202507\code\AIMS4PT\paper\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF4DA95-3DE0-4FE9-A42C-CB6AB1A00978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01FE4F8-5807-4C2E-9188-57F2422D81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1880" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9180" yWindow="4170" windowWidth="28800" windowHeight="15080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2112,7 +2112,7 @@
     <col min="1" max="1" width="28.90625" customWidth="1"/>
     <col min="2" max="2" width="19.453125" customWidth="1"/>
     <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -2193,8 +2193,8 @@
       <c r="D2">
         <v>2006</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>540</v>
+      <c r="E2" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F2" t="s">
         <v>491</v>
@@ -2252,8 +2252,8 @@
       <c r="D3">
         <v>2006</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>540</v>
+      <c r="E3" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F3" t="s">
         <v>491</v>
@@ -2311,8 +2311,8 @@
       <c r="D4">
         <v>2006</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>540</v>
+      <c r="E4" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F4" t="s">
         <v>491</v>
@@ -2370,8 +2370,8 @@
       <c r="D5">
         <v>2006</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>540</v>
+      <c r="E5" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F5" t="s">
         <v>491</v>
@@ -2429,8 +2429,8 @@
       <c r="D6">
         <v>2006</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>540</v>
+      <c r="E6" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F6" t="s">
         <v>491</v>
@@ -2488,8 +2488,8 @@
       <c r="D7">
         <v>2006</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>540</v>
+      <c r="E7" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F7" t="s">
         <v>492</v>
@@ -2547,8 +2547,8 @@
       <c r="D8">
         <v>2006</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>540</v>
+      <c r="E8" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F8" t="s">
         <v>492</v>
@@ -2606,8 +2606,8 @@
       <c r="D9">
         <v>2006</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>540</v>
+      <c r="E9" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F9" t="s">
         <v>492</v>
@@ -2665,8 +2665,8 @@
       <c r="D10">
         <v>2006</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>540</v>
+      <c r="E10" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F10" t="s">
         <v>492</v>
@@ -2724,8 +2724,8 @@
       <c r="D11">
         <v>2006</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>540</v>
+      <c r="E11" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F11" t="s">
         <v>492</v>
@@ -2783,8 +2783,8 @@
       <c r="D12">
         <v>2006</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>540</v>
+      <c r="E12" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F12" t="s">
         <v>492</v>
@@ -2842,8 +2842,8 @@
       <c r="D13">
         <v>2006</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>540</v>
+      <c r="E13" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F13" t="s">
         <v>492</v>
@@ -2901,8 +2901,8 @@
       <c r="D14">
         <v>2006</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>540</v>
+      <c r="E14" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F14" t="s">
         <v>492</v>
@@ -2960,8 +2960,8 @@
       <c r="D15">
         <v>2006</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>540</v>
+      <c r="E15" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F15" t="s">
         <v>492</v>
@@ -3019,8 +3019,8 @@
       <c r="D16">
         <v>2006</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>540</v>
+      <c r="E16" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F16" t="s">
         <v>492</v>
@@ -3078,8 +3078,8 @@
       <c r="D17">
         <v>2006</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>540</v>
+      <c r="E17" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F17" t="s">
         <v>492</v>
@@ -3137,8 +3137,8 @@
       <c r="D18">
         <v>2006</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>540</v>
+      <c r="E18" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F18" t="s">
         <v>492</v>
@@ -3196,8 +3196,8 @@
       <c r="D19">
         <v>2006</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>540</v>
+      <c r="E19" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F19" t="s">
         <v>492</v>
@@ -3255,8 +3255,8 @@
       <c r="D20">
         <v>2006</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>540</v>
+      <c r="E20" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F20" t="s">
         <v>492</v>
@@ -3314,8 +3314,8 @@
       <c r="D21">
         <v>2006</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>540</v>
+      <c r="E21" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F21" t="s">
         <v>492</v>
@@ -3373,8 +3373,8 @@
       <c r="D22">
         <v>2006</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>540</v>
+      <c r="E22" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>491</v>
@@ -3432,8 +3432,8 @@
       <c r="D23">
         <v>2006</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>540</v>
+      <c r="E23" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>491</v>
@@ -3491,8 +3491,8 @@
       <c r="D24">
         <v>2006</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>540</v>
+      <c r="E24" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>491</v>
@@ -3550,8 +3550,8 @@
       <c r="D25">
         <v>2006</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>540</v>
+      <c r="E25" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>491</v>
@@ -3609,8 +3609,8 @@
       <c r="D26">
         <v>2006</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>540</v>
+      <c r="E26" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>491</v>
@@ -3668,8 +3668,8 @@
       <c r="D27">
         <v>2006</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>540</v>
+      <c r="E27" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>491</v>
@@ -3727,8 +3727,8 @@
       <c r="D28">
         <v>2006</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>540</v>
+      <c r="E28" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>491</v>
@@ -3786,8 +3786,8 @@
       <c r="D29">
         <v>2006</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>540</v>
+      <c r="E29" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>491</v>
@@ -3845,8 +3845,8 @@
       <c r="D30">
         <v>2006</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>540</v>
+      <c r="E30" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>491</v>
@@ -3904,8 +3904,8 @@
       <c r="D31">
         <v>2006</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>540</v>
+      <c r="E31" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>491</v>
@@ -3963,8 +3963,8 @@
       <c r="D32">
         <v>2006</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>540</v>
+      <c r="E32" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>491</v>
@@ -4022,8 +4022,8 @@
       <c r="D33">
         <v>2006</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>540</v>
+      <c r="E33" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>491</v>
@@ -4081,8 +4081,8 @@
       <c r="D34">
         <v>2006</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>540</v>
+      <c r="E34" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>491</v>
@@ -4140,8 +4140,8 @@
       <c r="D35">
         <v>2006</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>540</v>
+      <c r="E35" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>491</v>
@@ -4199,8 +4199,8 @@
       <c r="D36">
         <v>2006</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>540</v>
+      <c r="E36" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>491</v>
@@ -4258,8 +4258,8 @@
       <c r="D37">
         <v>2006</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>540</v>
+      <c r="E37" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>491</v>
@@ -4317,8 +4317,8 @@
       <c r="D38">
         <v>2006</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>540</v>
+      <c r="E38" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>491</v>
@@ -4376,8 +4376,8 @@
       <c r="D39">
         <v>2006</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>540</v>
+      <c r="E39" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>491</v>
@@ -4435,8 +4435,8 @@
       <c r="D40">
         <v>2006</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>540</v>
+      <c r="E40" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>491</v>
@@ -4494,8 +4494,8 @@
       <c r="D41">
         <v>2006</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>540</v>
+      <c r="E41" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>491</v>
@@ -4553,8 +4553,8 @@
       <c r="D42">
         <v>2006</v>
       </c>
-      <c r="E42" s="9" t="s">
-        <v>540</v>
+      <c r="E42" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>491</v>
@@ -4612,8 +4612,8 @@
       <c r="D43">
         <v>2006</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>540</v>
+      <c r="E43" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>491</v>
@@ -4671,8 +4671,8 @@
       <c r="D44">
         <v>2006</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>540</v>
+      <c r="E44" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>491</v>
@@ -4730,8 +4730,8 @@
       <c r="D45">
         <v>2006</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>540</v>
+      <c r="E45" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>491</v>
@@ -4789,8 +4789,8 @@
       <c r="D46">
         <v>2006</v>
       </c>
-      <c r="E46" s="9" t="s">
-        <v>540</v>
+      <c r="E46" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>491</v>
@@ -4848,8 +4848,8 @@
       <c r="D47">
         <v>2006</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>540</v>
+      <c r="E47" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>492</v>
@@ -4907,8 +4907,8 @@
       <c r="D48">
         <v>2006</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>540</v>
+      <c r="E48" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>492</v>
@@ -4966,8 +4966,8 @@
       <c r="D49">
         <v>2006</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>540</v>
+      <c r="E49" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>492</v>
@@ -5025,8 +5025,8 @@
       <c r="D50">
         <v>2006</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>540</v>
+      <c r="E50" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>492</v>
@@ -5084,8 +5084,8 @@
       <c r="D51">
         <v>2006</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>540</v>
+      <c r="E51" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>492</v>
@@ -5143,8 +5143,8 @@
       <c r="D52">
         <v>2006</v>
       </c>
-      <c r="E52" s="9" t="s">
-        <v>540</v>
+      <c r="E52" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>492</v>
@@ -5202,8 +5202,8 @@
       <c r="D53">
         <v>2006</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>540</v>
+      <c r="E53" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>492</v>
@@ -5261,8 +5261,8 @@
       <c r="D54">
         <v>2006</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>540</v>
+      <c r="E54" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>492</v>
@@ -5320,8 +5320,8 @@
       <c r="D55">
         <v>2006</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>540</v>
+      <c r="E55" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>492</v>
@@ -5379,8 +5379,8 @@
       <c r="D56">
         <v>2006</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>540</v>
+      <c r="E56" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>492</v>
@@ -5438,8 +5438,8 @@
       <c r="D57">
         <v>2006</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>540</v>
+      <c r="E57" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>492</v>
@@ -5497,8 +5497,8 @@
       <c r="D58">
         <v>2006</v>
       </c>
-      <c r="E58" s="9" t="s">
-        <v>540</v>
+      <c r="E58" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>492</v>
@@ -5556,8 +5556,8 @@
       <c r="D59">
         <v>2006</v>
       </c>
-      <c r="E59" s="9" t="s">
-        <v>540</v>
+      <c r="E59" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>492</v>
@@ -5615,8 +5615,8 @@
       <c r="D60">
         <v>2006</v>
       </c>
-      <c r="E60" s="9" t="s">
-        <v>540</v>
+      <c r="E60" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>491</v>
@@ -5674,8 +5674,8 @@
       <c r="D61">
         <v>2006</v>
       </c>
-      <c r="E61" s="9" t="s">
-        <v>540</v>
+      <c r="E61" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>491</v>
@@ -5733,8 +5733,8 @@
       <c r="D62">
         <v>2006</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>540</v>
+      <c r="E62" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>491</v>
@@ -5792,8 +5792,8 @@
       <c r="D63">
         <v>2006</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>540</v>
+      <c r="E63" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>491</v>
@@ -5851,8 +5851,8 @@
       <c r="D64">
         <v>2006</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>540</v>
+      <c r="E64" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>491</v>
@@ -5910,8 +5910,8 @@
       <c r="D65">
         <v>2006</v>
       </c>
-      <c r="E65" s="9" t="s">
-        <v>540</v>
+      <c r="E65" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>491</v>
@@ -5969,8 +5969,8 @@
       <c r="D66">
         <v>2006</v>
       </c>
-      <c r="E66" s="9" t="s">
-        <v>540</v>
+      <c r="E66" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>491</v>
@@ -6028,8 +6028,8 @@
       <c r="D67">
         <v>2006</v>
       </c>
-      <c r="E67" s="9" t="s">
-        <v>540</v>
+      <c r="E67" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>491</v>
@@ -6087,8 +6087,8 @@
       <c r="D68">
         <v>2006</v>
       </c>
-      <c r="E68" s="9" t="s">
-        <v>540</v>
+      <c r="E68" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>491</v>
@@ -6146,8 +6146,8 @@
       <c r="D69">
         <v>2006</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>540</v>
+      <c r="E69" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>491</v>
@@ -6205,8 +6205,8 @@
       <c r="D70">
         <v>2006</v>
       </c>
-      <c r="E70" s="9" t="s">
-        <v>540</v>
+      <c r="E70" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>491</v>
@@ -6264,8 +6264,8 @@
       <c r="D71">
         <v>2006</v>
       </c>
-      <c r="E71" s="9" t="s">
-        <v>540</v>
+      <c r="E71" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>491</v>
@@ -6323,8 +6323,8 @@
       <c r="D72">
         <v>2006</v>
       </c>
-      <c r="E72" s="9" t="s">
-        <v>540</v>
+      <c r="E72" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>491</v>
@@ -6382,8 +6382,8 @@
       <c r="D73">
         <v>2006</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>540</v>
+      <c r="E73" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>491</v>
@@ -6441,8 +6441,8 @@
       <c r="D74">
         <v>2006</v>
       </c>
-      <c r="E74" s="9" t="s">
-        <v>540</v>
+      <c r="E74" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>491</v>
@@ -6500,8 +6500,8 @@
       <c r="D75">
         <v>2006</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>540</v>
+      <c r="E75" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>491</v>
@@ -6559,8 +6559,8 @@
       <c r="D76">
         <v>2006</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>540</v>
+      <c r="E76" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>491</v>
@@ -6618,8 +6618,8 @@
       <c r="D77">
         <v>2006</v>
       </c>
-      <c r="E77" s="9" t="s">
-        <v>540</v>
+      <c r="E77" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>491</v>
@@ -6677,8 +6677,8 @@
       <c r="D78">
         <v>2006</v>
       </c>
-      <c r="E78" s="9" t="s">
-        <v>540</v>
+      <c r="E78" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>491</v>
@@ -6736,8 +6736,8 @@
       <c r="D79">
         <v>2006</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>540</v>
+      <c r="E79" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>491</v>
@@ -6795,8 +6795,8 @@
       <c r="D80">
         <v>2006</v>
       </c>
-      <c r="E80" s="9" t="s">
-        <v>540</v>
+      <c r="E80" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>491</v>
@@ -6854,8 +6854,8 @@
       <c r="D81">
         <v>2006</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>540</v>
+      <c r="E81" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>491</v>
@@ -6913,8 +6913,8 @@
       <c r="D82">
         <v>2006</v>
       </c>
-      <c r="E82" s="9" t="s">
-        <v>540</v>
+      <c r="E82" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>491</v>
@@ -6972,8 +6972,8 @@
       <c r="D83">
         <v>2006</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>540</v>
+      <c r="E83" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>491</v>
@@ -7031,8 +7031,8 @@
       <c r="D84">
         <v>2006</v>
       </c>
-      <c r="E84" s="9" t="s">
-        <v>540</v>
+      <c r="E84" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>491</v>
@@ -7090,8 +7090,8 @@
       <c r="D85">
         <v>2006</v>
       </c>
-      <c r="E85" s="9" t="s">
-        <v>540</v>
+      <c r="E85" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>491</v>
@@ -7149,8 +7149,8 @@
       <c r="D86">
         <v>2006</v>
       </c>
-      <c r="E86" s="9" t="s">
-        <v>540</v>
+      <c r="E86" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>491</v>
@@ -7208,8 +7208,8 @@
       <c r="D87">
         <v>2006</v>
       </c>
-      <c r="E87" s="9" t="s">
-        <v>540</v>
+      <c r="E87" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>491</v>
@@ -7267,8 +7267,8 @@
       <c r="D88">
         <v>2006</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>540</v>
+      <c r="E88" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>491</v>
@@ -7326,8 +7326,8 @@
       <c r="D89">
         <v>2006</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>540</v>
+      <c r="E89" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>491</v>
@@ -7385,8 +7385,8 @@
       <c r="D90">
         <v>2006</v>
       </c>
-      <c r="E90" s="9" t="s">
-        <v>540</v>
+      <c r="E90" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>491</v>
@@ -7444,8 +7444,8 @@
       <c r="D91">
         <v>2006</v>
       </c>
-      <c r="E91" s="9" t="s">
-        <v>540</v>
+      <c r="E91" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>491</v>
@@ -7503,8 +7503,8 @@
       <c r="D92">
         <v>2006</v>
       </c>
-      <c r="E92" s="9" t="s">
-        <v>540</v>
+      <c r="E92" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>491</v>
@@ -7562,8 +7562,8 @@
       <c r="D93">
         <v>2006</v>
       </c>
-      <c r="E93" s="9" t="s">
-        <v>540</v>
+      <c r="E93" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>491</v>
@@ -7621,8 +7621,8 @@
       <c r="D94">
         <v>2006</v>
       </c>
-      <c r="E94" s="9" t="s">
-        <v>540</v>
+      <c r="E94" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>491</v>
@@ -7680,8 +7680,8 @@
       <c r="D95">
         <v>2006</v>
       </c>
-      <c r="E95" s="9" t="s">
-        <v>540</v>
+      <c r="E95" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>491</v>
@@ -7739,8 +7739,8 @@
       <c r="D96">
         <v>2006</v>
       </c>
-      <c r="E96" s="9" t="s">
-        <v>540</v>
+      <c r="E96" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F96" t="s">
         <v>492</v>
@@ -7798,8 +7798,8 @@
       <c r="D97">
         <v>2006</v>
       </c>
-      <c r="E97" s="9" t="s">
-        <v>540</v>
+      <c r="E97" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F97" t="s">
         <v>492</v>
@@ -7857,8 +7857,8 @@
       <c r="D98">
         <v>2006</v>
       </c>
-      <c r="E98" s="9" t="s">
-        <v>540</v>
+      <c r="E98" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F98" t="s">
         <v>492</v>
@@ -7916,8 +7916,8 @@
       <c r="D99">
         <v>2006</v>
       </c>
-      <c r="E99" s="9" t="s">
-        <v>540</v>
+      <c r="E99" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F99" t="s">
         <v>492</v>
@@ -7975,8 +7975,8 @@
       <c r="D100">
         <v>2006</v>
       </c>
-      <c r="E100" s="9" t="s">
-        <v>540</v>
+      <c r="E100" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F100" t="s">
         <v>492</v>
@@ -8034,8 +8034,8 @@
       <c r="D101">
         <v>2006</v>
       </c>
-      <c r="E101" s="9" t="s">
-        <v>540</v>
+      <c r="E101" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F101" t="s">
         <v>492</v>
@@ -8093,8 +8093,8 @@
       <c r="D102">
         <v>2006</v>
       </c>
-      <c r="E102" s="9" t="s">
-        <v>540</v>
+      <c r="E102" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F102" t="s">
         <v>492</v>
@@ -8152,8 +8152,8 @@
       <c r="D103">
         <v>2006</v>
       </c>
-      <c r="E103" s="9" t="s">
-        <v>540</v>
+      <c r="E103" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F103" t="s">
         <v>492</v>
@@ -8211,8 +8211,8 @@
       <c r="D104">
         <v>2006</v>
       </c>
-      <c r="E104" s="9" t="s">
-        <v>540</v>
+      <c r="E104" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F104" t="s">
         <v>492</v>
@@ -8270,8 +8270,8 @@
       <c r="D105">
         <v>2006</v>
       </c>
-      <c r="E105" s="9" t="s">
-        <v>540</v>
+      <c r="E105" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F105" t="s">
         <v>492</v>
@@ -8329,8 +8329,8 @@
       <c r="D106">
         <v>2006</v>
       </c>
-      <c r="E106" s="9" t="s">
-        <v>540</v>
+      <c r="E106" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F106" t="s">
         <v>492</v>
@@ -8388,8 +8388,8 @@
       <c r="D107">
         <v>2006</v>
       </c>
-      <c r="E107" s="9" t="s">
-        <v>540</v>
+      <c r="E107" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F107" t="s">
         <v>492</v>
@@ -8447,8 +8447,8 @@
       <c r="D108">
         <v>2006</v>
       </c>
-      <c r="E108" s="9" t="s">
-        <v>540</v>
+      <c r="E108" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F108" t="s">
         <v>492</v>
@@ -8506,8 +8506,8 @@
       <c r="D109">
         <v>2006</v>
       </c>
-      <c r="E109" s="9" t="s">
-        <v>540</v>
+      <c r="E109" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F109" t="s">
         <v>492</v>
@@ -8565,8 +8565,8 @@
       <c r="D110">
         <v>2006</v>
       </c>
-      <c r="E110" s="9" t="s">
-        <v>540</v>
+      <c r="E110" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F110" t="s">
         <v>491</v>
@@ -8624,8 +8624,8 @@
       <c r="D111">
         <v>2006</v>
       </c>
-      <c r="E111" s="9" t="s">
-        <v>540</v>
+      <c r="E111" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F111" t="s">
         <v>491</v>
@@ -8683,8 +8683,8 @@
       <c r="D112">
         <v>2006</v>
       </c>
-      <c r="E112" s="9" t="s">
-        <v>540</v>
+      <c r="E112" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F112" t="s">
         <v>491</v>
@@ -8742,8 +8742,8 @@
       <c r="D113">
         <v>2006</v>
       </c>
-      <c r="E113" s="9" t="s">
-        <v>540</v>
+      <c r="E113" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F113" t="s">
         <v>491</v>
@@ -8801,8 +8801,8 @@
       <c r="D114">
         <v>2006</v>
       </c>
-      <c r="E114" s="9" t="s">
-        <v>540</v>
+      <c r="E114" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F114" t="s">
         <v>491</v>
@@ -8860,8 +8860,8 @@
       <c r="D115">
         <v>2006</v>
       </c>
-      <c r="E115" s="9" t="s">
-        <v>540</v>
+      <c r="E115" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F115" t="s">
         <v>491</v>
@@ -8919,8 +8919,8 @@
       <c r="D116">
         <v>2006</v>
       </c>
-      <c r="E116" s="9" t="s">
-        <v>540</v>
+      <c r="E116" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F116" t="s">
         <v>491</v>
@@ -8978,8 +8978,8 @@
       <c r="D117">
         <v>2006</v>
       </c>
-      <c r="E117" s="9" t="s">
-        <v>540</v>
+      <c r="E117" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F117" t="s">
         <v>491</v>
@@ -9037,8 +9037,8 @@
       <c r="D118">
         <v>2006</v>
       </c>
-      <c r="E118" s="9" t="s">
-        <v>540</v>
+      <c r="E118" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F118" t="s">
         <v>491</v>
@@ -9096,8 +9096,8 @@
       <c r="D119">
         <v>2006</v>
       </c>
-      <c r="E119" s="9" t="s">
-        <v>540</v>
+      <c r="E119" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F119" t="s">
         <v>491</v>
@@ -9155,8 +9155,8 @@
       <c r="D120">
         <v>2006</v>
       </c>
-      <c r="E120" s="9" t="s">
-        <v>540</v>
+      <c r="E120" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F120" t="s">
         <v>491</v>
@@ -9214,8 +9214,8 @@
       <c r="D121">
         <v>2006</v>
       </c>
-      <c r="E121" s="9" t="s">
-        <v>540</v>
+      <c r="E121" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F121" t="s">
         <v>492</v>
@@ -9273,8 +9273,8 @@
       <c r="D122">
         <v>2006</v>
       </c>
-      <c r="E122" s="9" t="s">
-        <v>540</v>
+      <c r="E122" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F122" t="s">
         <v>492</v>
@@ -9332,8 +9332,8 @@
       <c r="D123">
         <v>2006</v>
       </c>
-      <c r="E123" s="9" t="s">
-        <v>540</v>
+      <c r="E123" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F123" t="s">
         <v>492</v>
@@ -9391,8 +9391,8 @@
       <c r="D124">
         <v>2006</v>
       </c>
-      <c r="E124" s="9" t="s">
-        <v>540</v>
+      <c r="E124" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F124" t="s">
         <v>492</v>
@@ -9450,8 +9450,8 @@
       <c r="D125">
         <v>2006</v>
       </c>
-      <c r="E125" s="9" t="s">
-        <v>540</v>
+      <c r="E125" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F125" t="s">
         <v>492</v>
@@ -9509,8 +9509,8 @@
       <c r="D126">
         <v>2006</v>
       </c>
-      <c r="E126" s="9" t="s">
-        <v>540</v>
+      <c r="E126" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F126" t="s">
         <v>492</v>
@@ -9568,8 +9568,8 @@
       <c r="D127">
         <v>2006</v>
       </c>
-      <c r="E127" s="9" t="s">
-        <v>540</v>
+      <c r="E127" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F127" t="s">
         <v>492</v>
@@ -9627,8 +9627,8 @@
       <c r="D128">
         <v>2006</v>
       </c>
-      <c r="E128" s="9" t="s">
-        <v>540</v>
+      <c r="E128" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F128" t="s">
         <v>492</v>
@@ -9686,8 +9686,8 @@
       <c r="D129">
         <v>2006</v>
       </c>
-      <c r="E129" s="9" t="s">
-        <v>540</v>
+      <c r="E129" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F129" t="s">
         <v>492</v>
@@ -9745,8 +9745,8 @@
       <c r="D130">
         <v>2006</v>
       </c>
-      <c r="E130" s="9" t="s">
-        <v>540</v>
+      <c r="E130" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F130" t="s">
         <v>492</v>
@@ -9804,8 +9804,8 @@
       <c r="D131">
         <v>2006</v>
       </c>
-      <c r="E131" s="9" t="s">
-        <v>540</v>
+      <c r="E131" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F131" t="s">
         <v>492</v>
@@ -9863,8 +9863,8 @@
       <c r="D132">
         <v>2006</v>
       </c>
-      <c r="E132" s="9" t="s">
-        <v>540</v>
+      <c r="E132" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F132" t="s">
         <v>492</v>
@@ -9922,8 +9922,8 @@
       <c r="D133">
         <v>2006</v>
       </c>
-      <c r="E133" s="9" t="s">
-        <v>540</v>
+      <c r="E133" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F133" t="s">
         <v>492</v>
@@ -9981,8 +9981,8 @@
       <c r="D134">
         <v>2006</v>
       </c>
-      <c r="E134" s="9" t="s">
-        <v>540</v>
+      <c r="E134" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F134" t="s">
         <v>492</v>
@@ -10040,8 +10040,8 @@
       <c r="D135">
         <v>2006</v>
       </c>
-      <c r="E135" s="9" t="s">
-        <v>540</v>
+      <c r="E135" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F135" t="s">
         <v>492</v>
@@ -10099,8 +10099,8 @@
       <c r="D136">
         <v>2006</v>
       </c>
-      <c r="E136" s="9" t="s">
-        <v>540</v>
+      <c r="E136" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F136" t="s">
         <v>492</v>
@@ -10158,8 +10158,8 @@
       <c r="D137">
         <v>2010</v>
       </c>
-      <c r="E137" s="9" t="s">
-        <v>540</v>
+      <c r="E137" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F137" t="s">
         <v>491</v>
@@ -10217,8 +10217,8 @@
       <c r="D138">
         <v>2010</v>
       </c>
-      <c r="E138" s="9" t="s">
-        <v>540</v>
+      <c r="E138" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F138" t="s">
         <v>491</v>
@@ -10276,8 +10276,8 @@
       <c r="D139">
         <v>2010</v>
       </c>
-      <c r="E139" s="9" t="s">
-        <v>540</v>
+      <c r="E139" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F139" t="s">
         <v>491</v>
@@ -10335,8 +10335,8 @@
       <c r="D140">
         <v>2010</v>
       </c>
-      <c r="E140" s="9" t="s">
-        <v>540</v>
+      <c r="E140" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F140" t="s">
         <v>491</v>
@@ -10394,8 +10394,8 @@
       <c r="D141">
         <v>2010</v>
       </c>
-      <c r="E141" s="9" t="s">
-        <v>540</v>
+      <c r="E141" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F141" t="s">
         <v>491</v>
@@ -10453,8 +10453,8 @@
       <c r="D142">
         <v>2010</v>
       </c>
-      <c r="E142" s="9" t="s">
-        <v>540</v>
+      <c r="E142" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F142" t="s">
         <v>491</v>
@@ -10512,8 +10512,8 @@
       <c r="D143">
         <v>2010</v>
       </c>
-      <c r="E143" s="9" t="s">
-        <v>540</v>
+      <c r="E143" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F143" t="s">
         <v>491</v>
@@ -10571,8 +10571,8 @@
       <c r="D144">
         <v>2010</v>
       </c>
-      <c r="E144" s="9" t="s">
-        <v>540</v>
+      <c r="E144" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F144" t="s">
         <v>491</v>
@@ -10630,8 +10630,8 @@
       <c r="D145">
         <v>2010</v>
       </c>
-      <c r="E145" s="9" t="s">
-        <v>540</v>
+      <c r="E145" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F145" t="s">
         <v>491</v>
@@ -10689,8 +10689,8 @@
       <c r="D146">
         <v>2010</v>
       </c>
-      <c r="E146" s="9" t="s">
-        <v>540</v>
+      <c r="E146" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F146" t="s">
         <v>491</v>
@@ -10748,8 +10748,8 @@
       <c r="D147">
         <v>2010</v>
       </c>
-      <c r="E147" s="9" t="s">
-        <v>540</v>
+      <c r="E147" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F147" t="s">
         <v>491</v>
@@ -10807,8 +10807,8 @@
       <c r="D148">
         <v>2010</v>
       </c>
-      <c r="E148" s="9" t="s">
-        <v>540</v>
+      <c r="E148" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F148" t="s">
         <v>491</v>
@@ -10866,8 +10866,8 @@
       <c r="D149">
         <v>2010</v>
       </c>
-      <c r="E149" s="9" t="s">
-        <v>540</v>
+      <c r="E149" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F149" t="s">
         <v>491</v>
@@ -10925,8 +10925,8 @@
       <c r="D150">
         <v>2010</v>
       </c>
-      <c r="E150" s="9" t="s">
-        <v>540</v>
+      <c r="E150" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F150" t="s">
         <v>491</v>
@@ -10984,8 +10984,8 @@
       <c r="D151">
         <v>2010</v>
       </c>
-      <c r="E151" s="9" t="s">
-        <v>540</v>
+      <c r="E151" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F151" t="s">
         <v>491</v>
@@ -11043,8 +11043,8 @@
       <c r="D152">
         <v>2010</v>
       </c>
-      <c r="E152" s="9" t="s">
-        <v>540</v>
+      <c r="E152" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F152" t="s">
         <v>491</v>
@@ -11102,8 +11102,8 @@
       <c r="D153">
         <v>2010</v>
       </c>
-      <c r="E153" s="9" t="s">
-        <v>540</v>
+      <c r="E153" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F153" t="s">
         <v>491</v>
@@ -11161,8 +11161,8 @@
       <c r="D154">
         <v>2010</v>
       </c>
-      <c r="E154" s="9" t="s">
-        <v>540</v>
+      <c r="E154" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F154" t="s">
         <v>492</v>
@@ -11220,8 +11220,8 @@
       <c r="D155">
         <v>2010</v>
       </c>
-      <c r="E155" s="9" t="s">
-        <v>540</v>
+      <c r="E155" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F155" t="s">
         <v>492</v>
@@ -11279,8 +11279,8 @@
       <c r="D156">
         <v>2010</v>
       </c>
-      <c r="E156" s="9" t="s">
-        <v>540</v>
+      <c r="E156" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F156" t="s">
         <v>492</v>
@@ -11338,8 +11338,8 @@
       <c r="D157">
         <v>2010</v>
       </c>
-      <c r="E157" s="9" t="s">
-        <v>540</v>
+      <c r="E157" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F157" t="s">
         <v>492</v>
@@ -11397,8 +11397,8 @@
       <c r="D158">
         <v>2010</v>
       </c>
-      <c r="E158" s="9" t="s">
-        <v>540</v>
+      <c r="E158" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F158" t="s">
         <v>492</v>
@@ -11456,8 +11456,8 @@
       <c r="D159">
         <v>2010</v>
       </c>
-      <c r="E159" s="9" t="s">
-        <v>540</v>
+      <c r="E159" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F159" t="s">
         <v>492</v>
@@ -11515,8 +11515,8 @@
       <c r="D160">
         <v>2010</v>
       </c>
-      <c r="E160" s="9" t="s">
-        <v>540</v>
+      <c r="E160" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F160" t="s">
         <v>492</v>
@@ -11574,8 +11574,8 @@
       <c r="D161">
         <v>2010</v>
       </c>
-      <c r="E161" s="9" t="s">
-        <v>540</v>
+      <c r="E161" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F161" t="s">
         <v>492</v>
@@ -11633,8 +11633,8 @@
       <c r="D162">
         <v>2010</v>
       </c>
-      <c r="E162" s="9" t="s">
-        <v>540</v>
+      <c r="E162" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F162" t="s">
         <v>492</v>
@@ -11692,8 +11692,8 @@
       <c r="D163">
         <v>2010</v>
       </c>
-      <c r="E163" s="9" t="s">
-        <v>540</v>
+      <c r="E163" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F163" t="s">
         <v>492</v>
@@ -11751,8 +11751,8 @@
       <c r="D164">
         <v>2010</v>
       </c>
-      <c r="E164" s="9" t="s">
-        <v>540</v>
+      <c r="E164" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F164" t="s">
         <v>492</v>
@@ -11810,8 +11810,8 @@
       <c r="D165">
         <v>2010</v>
       </c>
-      <c r="E165" s="9" t="s">
-        <v>540</v>
+      <c r="E165" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F165" t="s">
         <v>492</v>
@@ -11869,8 +11869,8 @@
       <c r="D166">
         <v>2010</v>
       </c>
-      <c r="E166" s="9" t="s">
-        <v>540</v>
+      <c r="E166" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F166" t="s">
         <v>492</v>
@@ -11928,8 +11928,8 @@
       <c r="D167">
         <v>2010</v>
       </c>
-      <c r="E167" s="9" t="s">
-        <v>540</v>
+      <c r="E167" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F167" t="s">
         <v>492</v>
@@ -11987,8 +11987,8 @@
       <c r="D168">
         <v>2010</v>
       </c>
-      <c r="E168" s="9" t="s">
-        <v>540</v>
+      <c r="E168" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F168" t="s">
         <v>492</v>
@@ -12046,8 +12046,8 @@
       <c r="D169">
         <v>2010</v>
       </c>
-      <c r="E169" s="9" t="s">
-        <v>540</v>
+      <c r="E169" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F169" t="s">
         <v>492</v>
@@ -12105,8 +12105,8 @@
       <c r="D170">
         <v>2010</v>
       </c>
-      <c r="E170" s="9" t="s">
-        <v>540</v>
+      <c r="E170" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F170" t="s">
         <v>492</v>
@@ -12164,8 +12164,8 @@
       <c r="D171">
         <v>2010</v>
       </c>
-      <c r="E171" s="9" t="s">
-        <v>540</v>
+      <c r="E171" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F171" t="s">
         <v>492</v>
@@ -12223,8 +12223,8 @@
       <c r="D172">
         <v>2010</v>
       </c>
-      <c r="E172" s="9" t="s">
-        <v>540</v>
+      <c r="E172" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F172" t="s">
         <v>492</v>
@@ -12282,8 +12282,8 @@
       <c r="D173">
         <v>2010</v>
       </c>
-      <c r="E173" s="9" t="s">
-        <v>540</v>
+      <c r="E173" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F173" t="s">
         <v>492</v>
@@ -12341,8 +12341,8 @@
       <c r="D174">
         <v>2010</v>
       </c>
-      <c r="E174" s="9" t="s">
-        <v>540</v>
+      <c r="E174" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F174" t="s">
         <v>492</v>
@@ -12400,8 +12400,8 @@
       <c r="D175">
         <v>2010</v>
       </c>
-      <c r="E175" s="9" t="s">
-        <v>540</v>
+      <c r="E175" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F175" t="s">
         <v>492</v>
@@ -12459,8 +12459,8 @@
       <c r="D176">
         <v>2010</v>
       </c>
-      <c r="E176" s="9" t="s">
-        <v>540</v>
+      <c r="E176" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F176" t="s">
         <v>492</v>
@@ -12518,8 +12518,8 @@
       <c r="D177">
         <v>2010</v>
       </c>
-      <c r="E177" s="9" t="s">
-        <v>540</v>
+      <c r="E177" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F177" t="s">
         <v>492</v>
@@ -12577,8 +12577,8 @@
       <c r="D178">
         <v>2010</v>
       </c>
-      <c r="E178" s="9" t="s">
-        <v>540</v>
+      <c r="E178" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F178" t="s">
         <v>492</v>
@@ -12636,8 +12636,8 @@
       <c r="D179">
         <v>2010</v>
       </c>
-      <c r="E179" s="9" t="s">
-        <v>540</v>
+      <c r="E179" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F179" t="s">
         <v>492</v>
@@ -12695,8 +12695,8 @@
       <c r="D180">
         <v>2010</v>
       </c>
-      <c r="E180" s="9" t="s">
-        <v>540</v>
+      <c r="E180" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F180" t="s">
         <v>492</v>
@@ -12754,8 +12754,8 @@
       <c r="D181">
         <v>2010</v>
       </c>
-      <c r="E181" s="9" t="s">
-        <v>540</v>
+      <c r="E181" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F181" t="s">
         <v>492</v>
@@ -12813,8 +12813,8 @@
       <c r="D182">
         <v>2010</v>
       </c>
-      <c r="E182" s="9" t="s">
-        <v>540</v>
+      <c r="E182" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F182" t="s">
         <v>492</v>
@@ -12872,8 +12872,8 @@
       <c r="D183">
         <v>2010</v>
       </c>
-      <c r="E183" s="9" t="s">
-        <v>540</v>
+      <c r="E183" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F183" t="s">
         <v>492</v>
@@ -12931,8 +12931,8 @@
       <c r="D184">
         <v>2010</v>
       </c>
-      <c r="E184" s="9" t="s">
-        <v>540</v>
+      <c r="E184" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F184" t="s">
         <v>492</v>
@@ -12990,8 +12990,8 @@
       <c r="D185">
         <v>2010</v>
       </c>
-      <c r="E185" s="9" t="s">
-        <v>540</v>
+      <c r="E185" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F185" t="s">
         <v>492</v>
@@ -13049,8 +13049,8 @@
       <c r="D186">
         <v>2010</v>
       </c>
-      <c r="E186" s="9" t="s">
-        <v>540</v>
+      <c r="E186" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F186" t="s">
         <v>492</v>
@@ -13108,8 +13108,8 @@
       <c r="D187">
         <v>2010</v>
       </c>
-      <c r="E187" s="9" t="s">
-        <v>540</v>
+      <c r="E187" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F187" t="s">
         <v>492</v>
@@ -13167,8 +13167,8 @@
       <c r="D188">
         <v>2010</v>
       </c>
-      <c r="E188" s="9" t="s">
-        <v>540</v>
+      <c r="E188" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F188" t="s">
         <v>492</v>
@@ -13226,8 +13226,8 @@
       <c r="D189">
         <v>2010</v>
       </c>
-      <c r="E189" s="9" t="s">
-        <v>540</v>
+      <c r="E189" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F189" t="s">
         <v>492</v>
@@ -13285,8 +13285,8 @@
       <c r="D190">
         <v>2010</v>
       </c>
-      <c r="E190" s="9" t="s">
-        <v>540</v>
+      <c r="E190" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F190" t="s">
         <v>492</v>
@@ -13344,8 +13344,8 @@
       <c r="D191">
         <v>2010</v>
       </c>
-      <c r="E191" s="9" t="s">
-        <v>540</v>
+      <c r="E191" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F191" t="s">
         <v>492</v>
@@ -13403,8 +13403,8 @@
       <c r="D192">
         <v>2010</v>
       </c>
-      <c r="E192" s="9" t="s">
-        <v>540</v>
+      <c r="E192" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F192" t="s">
         <v>492</v>
@@ -13462,8 +13462,8 @@
       <c r="D193">
         <v>2010</v>
       </c>
-      <c r="E193" s="9" t="s">
-        <v>540</v>
+      <c r="E193" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F193" t="s">
         <v>492</v>
@@ -13521,8 +13521,8 @@
       <c r="D194">
         <v>2010</v>
       </c>
-      <c r="E194" s="9" t="s">
-        <v>540</v>
+      <c r="E194" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F194" t="s">
         <v>492</v>
@@ -13580,8 +13580,8 @@
       <c r="D195">
         <v>2010</v>
       </c>
-      <c r="E195" s="9" t="s">
-        <v>540</v>
+      <c r="E195" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F195" t="s">
         <v>492</v>
@@ -13639,8 +13639,8 @@
       <c r="D196">
         <v>2010</v>
       </c>
-      <c r="E196" s="9" t="s">
-        <v>540</v>
+      <c r="E196" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F196" t="s">
         <v>492</v>
@@ -13698,8 +13698,8 @@
       <c r="D197">
         <v>2010</v>
       </c>
-      <c r="E197" s="9" t="s">
-        <v>540</v>
+      <c r="E197" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F197" t="s">
         <v>492</v>
@@ -13757,8 +13757,8 @@
       <c r="D198">
         <v>2010</v>
       </c>
-      <c r="E198" s="9" t="s">
-        <v>540</v>
+      <c r="E198" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F198" t="s">
         <v>492</v>
@@ -13816,8 +13816,8 @@
       <c r="D199">
         <v>2010</v>
       </c>
-      <c r="E199" s="9" t="s">
-        <v>540</v>
+      <c r="E199" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F199" t="s">
         <v>492</v>
@@ -13875,8 +13875,8 @@
       <c r="D200">
         <v>2010</v>
       </c>
-      <c r="E200" s="9" t="s">
-        <v>540</v>
+      <c r="E200" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F200" t="s">
         <v>492</v>
@@ -13934,8 +13934,8 @@
       <c r="D201">
         <v>2010</v>
       </c>
-      <c r="E201" s="9" t="s">
-        <v>540</v>
+      <c r="E201" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F201" t="s">
         <v>492</v>
@@ -13993,8 +13993,8 @@
       <c r="D202">
         <v>2010</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>540</v>
+      <c r="E202" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F202" t="s">
         <v>492</v>
@@ -14052,8 +14052,8 @@
       <c r="D203">
         <v>2010</v>
       </c>
-      <c r="E203" s="9" t="s">
-        <v>540</v>
+      <c r="E203" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F203" t="s">
         <v>492</v>
@@ -14111,8 +14111,8 @@
       <c r="D204">
         <v>2010</v>
       </c>
-      <c r="E204" s="9" t="s">
-        <v>540</v>
+      <c r="E204" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F204" t="s">
         <v>492</v>
@@ -14170,8 +14170,8 @@
       <c r="D205">
         <v>2010</v>
       </c>
-      <c r="E205" s="9" t="s">
-        <v>540</v>
+      <c r="E205" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F205" t="s">
         <v>492</v>
@@ -14229,8 +14229,8 @@
       <c r="D206">
         <v>2010</v>
       </c>
-      <c r="E206" s="9" t="s">
-        <v>540</v>
+      <c r="E206" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F206" t="s">
         <v>492</v>
@@ -14288,8 +14288,8 @@
       <c r="D207">
         <v>2010</v>
       </c>
-      <c r="E207" s="9" t="s">
-        <v>540</v>
+      <c r="E207" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F207" t="s">
         <v>492</v>
@@ -14347,8 +14347,8 @@
       <c r="D208">
         <v>2010</v>
       </c>
-      <c r="E208" s="9" t="s">
-        <v>540</v>
+      <c r="E208" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F208" t="s">
         <v>492</v>
@@ -14406,8 +14406,8 @@
       <c r="D209">
         <v>2010</v>
       </c>
-      <c r="E209" s="9" t="s">
-        <v>540</v>
+      <c r="E209" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F209" t="s">
         <v>492</v>
@@ -14465,8 +14465,8 @@
       <c r="D210">
         <v>2010</v>
       </c>
-      <c r="E210" s="9" t="s">
-        <v>540</v>
+      <c r="E210" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F210" t="s">
         <v>492</v>
@@ -14524,8 +14524,8 @@
       <c r="D211">
         <v>2010</v>
       </c>
-      <c r="E211" s="9" t="s">
-        <v>540</v>
+      <c r="E211" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F211" t="s">
         <v>492</v>
@@ -14583,8 +14583,8 @@
       <c r="D212">
         <v>2010</v>
       </c>
-      <c r="E212" s="9" t="s">
-        <v>540</v>
+      <c r="E212" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F212" t="s">
         <v>492</v>
@@ -14642,8 +14642,8 @@
       <c r="D213">
         <v>2010</v>
       </c>
-      <c r="E213" s="9" t="s">
-        <v>540</v>
+      <c r="E213" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F213" t="s">
         <v>492</v>
@@ -14701,8 +14701,8 @@
       <c r="D214">
         <v>2010</v>
       </c>
-      <c r="E214" s="9" t="s">
-        <v>540</v>
+      <c r="E214" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F214" t="s">
         <v>492</v>
@@ -14760,8 +14760,8 @@
       <c r="D215">
         <v>2010</v>
       </c>
-      <c r="E215" s="9" t="s">
-        <v>540</v>
+      <c r="E215" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F215" t="s">
         <v>492</v>
@@ -14819,8 +14819,8 @@
       <c r="D216">
         <v>2010</v>
       </c>
-      <c r="E216" s="9" t="s">
-        <v>540</v>
+      <c r="E216" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F216" t="s">
         <v>492</v>
@@ -14878,8 +14878,8 @@
       <c r="D217">
         <v>2010</v>
       </c>
-      <c r="E217" s="9" t="s">
-        <v>540</v>
+      <c r="E217" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F217" t="s">
         <v>492</v>
@@ -14937,8 +14937,8 @@
       <c r="D218">
         <v>2010</v>
       </c>
-      <c r="E218" s="9" t="s">
-        <v>540</v>
+      <c r="E218" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F218" t="s">
         <v>492</v>
@@ -14996,8 +14996,8 @@
       <c r="D219">
         <v>2010</v>
       </c>
-      <c r="E219" s="9" t="s">
-        <v>540</v>
+      <c r="E219" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F219" t="s">
         <v>492</v>
@@ -15055,8 +15055,8 @@
       <c r="D220">
         <v>2010</v>
       </c>
-      <c r="E220" s="9" t="s">
-        <v>540</v>
+      <c r="E220" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F220" t="s">
         <v>492</v>
@@ -15114,8 +15114,8 @@
       <c r="D221">
         <v>2010</v>
       </c>
-      <c r="E221" s="9" t="s">
-        <v>540</v>
+      <c r="E221" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F221" t="s">
         <v>491</v>
@@ -15173,8 +15173,8 @@
       <c r="D222">
         <v>2010</v>
       </c>
-      <c r="E222" s="9" t="s">
-        <v>540</v>
+      <c r="E222" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F222" t="s">
         <v>491</v>
@@ -15232,8 +15232,8 @@
       <c r="D223">
         <v>2010</v>
       </c>
-      <c r="E223" s="9" t="s">
-        <v>540</v>
+      <c r="E223" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F223" t="s">
         <v>491</v>
@@ -15291,8 +15291,8 @@
       <c r="D224">
         <v>2010</v>
       </c>
-      <c r="E224" s="9" t="s">
-        <v>540</v>
+      <c r="E224" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F224" t="s">
         <v>491</v>
@@ -15350,8 +15350,8 @@
       <c r="D225">
         <v>2010</v>
       </c>
-      <c r="E225" s="9" t="s">
-        <v>540</v>
+      <c r="E225" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F225" t="s">
         <v>491</v>
@@ -15409,8 +15409,8 @@
       <c r="D226">
         <v>2010</v>
       </c>
-      <c r="E226" s="9" t="s">
-        <v>540</v>
+      <c r="E226" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F226" t="s">
         <v>491</v>
@@ -15468,8 +15468,8 @@
       <c r="D227">
         <v>2010</v>
       </c>
-      <c r="E227" s="9" t="s">
-        <v>540</v>
+      <c r="E227" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F227" t="s">
         <v>491</v>
@@ -15527,8 +15527,8 @@
       <c r="D228">
         <v>2010</v>
       </c>
-      <c r="E228" s="9" t="s">
-        <v>540</v>
+      <c r="E228" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F228" t="s">
         <v>491</v>
@@ -15586,8 +15586,8 @@
       <c r="D229">
         <v>2010</v>
       </c>
-      <c r="E229" s="9" t="s">
-        <v>540</v>
+      <c r="E229" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F229" t="s">
         <v>491</v>
@@ -15645,8 +15645,8 @@
       <c r="D230">
         <v>2010</v>
       </c>
-      <c r="E230" s="9" t="s">
-        <v>540</v>
+      <c r="E230" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F230" t="s">
         <v>491</v>
@@ -15704,8 +15704,8 @@
       <c r="D231">
         <v>2010</v>
       </c>
-      <c r="E231" s="9" t="s">
-        <v>540</v>
+      <c r="E231" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F231" t="s">
         <v>491</v>
@@ -15763,8 +15763,8 @@
       <c r="D232">
         <v>2010</v>
       </c>
-      <c r="E232" s="9" t="s">
-        <v>540</v>
+      <c r="E232" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F232" t="s">
         <v>491</v>
@@ -15822,8 +15822,8 @@
       <c r="D233">
         <v>2010</v>
       </c>
-      <c r="E233" s="9" t="s">
-        <v>540</v>
+      <c r="E233" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F233" t="s">
         <v>491</v>
@@ -15881,8 +15881,8 @@
       <c r="D234">
         <v>2010</v>
       </c>
-      <c r="E234" s="9" t="s">
-        <v>540</v>
+      <c r="E234" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F234" t="s">
         <v>491</v>
@@ -15940,8 +15940,8 @@
       <c r="D235">
         <v>2010</v>
       </c>
-      <c r="E235" s="9" t="s">
-        <v>540</v>
+      <c r="E235" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F235" t="s">
         <v>491</v>
@@ -15999,8 +15999,8 @@
       <c r="D236">
         <v>2010</v>
       </c>
-      <c r="E236" s="9" t="s">
-        <v>540</v>
+      <c r="E236" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F236" t="s">
         <v>491</v>
@@ -16058,8 +16058,8 @@
       <c r="D237">
         <v>2010</v>
       </c>
-      <c r="E237" s="9" t="s">
-        <v>540</v>
+      <c r="E237" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F237" t="s">
         <v>491</v>
@@ -16117,8 +16117,8 @@
       <c r="D238">
         <v>2010</v>
       </c>
-      <c r="E238" s="9" t="s">
-        <v>540</v>
+      <c r="E238" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F238" t="s">
         <v>492</v>
@@ -16176,8 +16176,8 @@
       <c r="D239">
         <v>2010</v>
       </c>
-      <c r="E239" s="9" t="s">
-        <v>540</v>
+      <c r="E239" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F239" t="s">
         <v>492</v>
@@ -16235,8 +16235,8 @@
       <c r="D240">
         <v>2010</v>
       </c>
-      <c r="E240" s="9" t="s">
-        <v>540</v>
+      <c r="E240" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F240" t="s">
         <v>492</v>
@@ -16294,8 +16294,8 @@
       <c r="D241">
         <v>2010</v>
       </c>
-      <c r="E241" s="9" t="s">
-        <v>540</v>
+      <c r="E241" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F241" t="s">
         <v>492</v>
@@ -16353,8 +16353,8 @@
       <c r="D242">
         <v>2010</v>
       </c>
-      <c r="E242" s="9" t="s">
-        <v>540</v>
+      <c r="E242" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F242" t="s">
         <v>492</v>
@@ -16412,8 +16412,8 @@
       <c r="D243">
         <v>2010</v>
       </c>
-      <c r="E243" s="9" t="s">
-        <v>540</v>
+      <c r="E243" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F243" t="s">
         <v>492</v>
@@ -16471,8 +16471,8 @@
       <c r="D244">
         <v>2010</v>
       </c>
-      <c r="E244" s="9" t="s">
-        <v>540</v>
+      <c r="E244" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F244" t="s">
         <v>492</v>
@@ -16530,8 +16530,8 @@
       <c r="D245">
         <v>2010</v>
       </c>
-      <c r="E245" s="9" t="s">
-        <v>540</v>
+      <c r="E245" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F245" t="s">
         <v>492</v>
@@ -16589,8 +16589,8 @@
       <c r="D246">
         <v>2010</v>
       </c>
-      <c r="E246" s="9" t="s">
-        <v>540</v>
+      <c r="E246" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F246" t="s">
         <v>492</v>
@@ -16648,8 +16648,8 @@
       <c r="D247">
         <v>2010</v>
       </c>
-      <c r="E247" s="9" t="s">
-        <v>540</v>
+      <c r="E247" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F247" t="s">
         <v>492</v>
@@ -16707,8 +16707,8 @@
       <c r="D248">
         <v>2010</v>
       </c>
-      <c r="E248" s="9" t="s">
-        <v>540</v>
+      <c r="E248" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F248" t="s">
         <v>492</v>
@@ -16766,8 +16766,8 @@
       <c r="D249">
         <v>2010</v>
       </c>
-      <c r="E249" s="9" t="s">
-        <v>540</v>
+      <c r="E249" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F249" t="s">
         <v>492</v>
@@ -16825,8 +16825,8 @@
       <c r="D250">
         <v>2010</v>
       </c>
-      <c r="E250" s="9" t="s">
-        <v>540</v>
+      <c r="E250" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F250" t="s">
         <v>492</v>
@@ -16884,8 +16884,8 @@
       <c r="D251">
         <v>2010</v>
       </c>
-      <c r="E251" s="9" t="s">
-        <v>540</v>
+      <c r="E251" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F251" t="s">
         <v>492</v>
@@ -16943,8 +16943,8 @@
       <c r="D252">
         <v>2010</v>
       </c>
-      <c r="E252" s="9" t="s">
-        <v>540</v>
+      <c r="E252" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F252" t="s">
         <v>492</v>
@@ -17002,8 +17002,8 @@
       <c r="D253">
         <v>2010</v>
       </c>
-      <c r="E253" s="9" t="s">
-        <v>540</v>
+      <c r="E253" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F253" t="s">
         <v>492</v>
@@ -17061,8 +17061,8 @@
       <c r="D254">
         <v>2010</v>
       </c>
-      <c r="E254" s="9" t="s">
-        <v>540</v>
+      <c r="E254" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F254" t="s">
         <v>492</v>
@@ -17120,8 +17120,8 @@
       <c r="D255">
         <v>2010</v>
       </c>
-      <c r="E255" s="9" t="s">
-        <v>540</v>
+      <c r="E255" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F255" t="s">
         <v>492</v>
@@ -17179,8 +17179,8 @@
       <c r="D256">
         <v>2010</v>
       </c>
-      <c r="E256" s="9" t="s">
-        <v>540</v>
+      <c r="E256" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F256" t="s">
         <v>492</v>
@@ -17238,8 +17238,8 @@
       <c r="D257">
         <v>2010</v>
       </c>
-      <c r="E257" s="9" t="s">
-        <v>540</v>
+      <c r="E257" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F257" t="s">
         <v>492</v>
@@ -17297,8 +17297,8 @@
       <c r="D258">
         <v>2010</v>
       </c>
-      <c r="E258" s="9" t="s">
-        <v>540</v>
+      <c r="E258" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F258" t="s">
         <v>492</v>
@@ -17356,8 +17356,8 @@
       <c r="D259">
         <v>2010</v>
       </c>
-      <c r="E259" s="9" t="s">
-        <v>540</v>
+      <c r="E259" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F259" t="s">
         <v>492</v>
@@ -17415,8 +17415,8 @@
       <c r="D260">
         <v>2010</v>
       </c>
-      <c r="E260" s="9" t="s">
-        <v>540</v>
+      <c r="E260" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F260" t="s">
         <v>492</v>
@@ -17474,8 +17474,8 @@
       <c r="D261">
         <v>2010</v>
       </c>
-      <c r="E261" s="9" t="s">
-        <v>540</v>
+      <c r="E261" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F261" t="s">
         <v>492</v>
@@ -17533,8 +17533,8 @@
       <c r="D262">
         <v>2010</v>
       </c>
-      <c r="E262" s="9" t="s">
-        <v>540</v>
+      <c r="E262" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F262" t="s">
         <v>492</v>
@@ -17592,8 +17592,8 @@
       <c r="D263">
         <v>2010</v>
       </c>
-      <c r="E263" s="9" t="s">
-        <v>540</v>
+      <c r="E263" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F263" t="s">
         <v>492</v>
@@ -17651,8 +17651,8 @@
       <c r="D264">
         <v>2010</v>
       </c>
-      <c r="E264" s="9" t="s">
-        <v>540</v>
+      <c r="E264" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F264" t="s">
         <v>492</v>
@@ -17710,8 +17710,8 @@
       <c r="D265">
         <v>2010</v>
       </c>
-      <c r="E265" s="9" t="s">
-        <v>540</v>
+      <c r="E265" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F265" t="s">
         <v>492</v>
@@ -17769,8 +17769,8 @@
       <c r="D266">
         <v>2010</v>
       </c>
-      <c r="E266" s="9" t="s">
-        <v>540</v>
+      <c r="E266" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F266" t="s">
         <v>492</v>
@@ -17828,8 +17828,8 @@
       <c r="D267">
         <v>2010</v>
       </c>
-      <c r="E267" s="9" t="s">
-        <v>540</v>
+      <c r="E267" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F267" t="s">
         <v>492</v>
@@ -17887,8 +17887,8 @@
       <c r="D268">
         <v>2010</v>
       </c>
-      <c r="E268" s="9" t="s">
-        <v>540</v>
+      <c r="E268" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F268" t="s">
         <v>492</v>
@@ -17946,8 +17946,8 @@
       <c r="D269">
         <v>2010</v>
       </c>
-      <c r="E269" s="9" t="s">
-        <v>540</v>
+      <c r="E269" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F269" t="s">
         <v>492</v>
@@ -18005,8 +18005,8 @@
       <c r="D270">
         <v>2010</v>
       </c>
-      <c r="E270" s="9" t="s">
-        <v>540</v>
+      <c r="E270" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F270" t="s">
         <v>492</v>
@@ -18064,8 +18064,8 @@
       <c r="D271">
         <v>2010</v>
       </c>
-      <c r="E271" s="9" t="s">
-        <v>540</v>
+      <c r="E271" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F271" t="s">
         <v>492</v>
@@ -18123,8 +18123,8 @@
       <c r="D272">
         <v>2010</v>
       </c>
-      <c r="E272" s="9" t="s">
-        <v>540</v>
+      <c r="E272" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F272" t="s">
         <v>491</v>
@@ -18182,8 +18182,8 @@
       <c r="D273">
         <v>2010</v>
       </c>
-      <c r="E273" s="9" t="s">
-        <v>540</v>
+      <c r="E273" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F273" t="s">
         <v>491</v>
@@ -18241,8 +18241,8 @@
       <c r="D274">
         <v>2010</v>
       </c>
-      <c r="E274" s="9" t="s">
-        <v>540</v>
+      <c r="E274" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F274" t="s">
         <v>491</v>
@@ -18300,8 +18300,8 @@
       <c r="D275">
         <v>2010</v>
       </c>
-      <c r="E275" s="9" t="s">
-        <v>540</v>
+      <c r="E275" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F275" t="s">
         <v>491</v>
@@ -18359,8 +18359,8 @@
       <c r="D276">
         <v>2010</v>
       </c>
-      <c r="E276" s="9" t="s">
-        <v>540</v>
+      <c r="E276" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F276" t="s">
         <v>491</v>
@@ -18418,8 +18418,8 @@
       <c r="D277">
         <v>2010</v>
       </c>
-      <c r="E277" s="9" t="s">
-        <v>540</v>
+      <c r="E277" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F277" t="s">
         <v>491</v>
@@ -18477,8 +18477,8 @@
       <c r="D278">
         <v>2010</v>
       </c>
-      <c r="E278" s="9" t="s">
-        <v>540</v>
+      <c r="E278" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F278" t="s">
         <v>491</v>
@@ -18536,8 +18536,8 @@
       <c r="D279">
         <v>2010</v>
       </c>
-      <c r="E279" s="9" t="s">
-        <v>540</v>
+      <c r="E279" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F279" t="s">
         <v>491</v>
@@ -18595,8 +18595,8 @@
       <c r="D280">
         <v>2010</v>
       </c>
-      <c r="E280" s="9" t="s">
-        <v>540</v>
+      <c r="E280" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F280" t="s">
         <v>492</v>
@@ -18654,8 +18654,8 @@
       <c r="D281">
         <v>2010</v>
       </c>
-      <c r="E281" s="9" t="s">
-        <v>540</v>
+      <c r="E281" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F281" t="s">
         <v>492</v>
@@ -18713,8 +18713,8 @@
       <c r="D282">
         <v>2010</v>
       </c>
-      <c r="E282" s="9" t="s">
-        <v>540</v>
+      <c r="E282" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F282" t="s">
         <v>492</v>
@@ -18772,8 +18772,8 @@
       <c r="D283">
         <v>2010</v>
       </c>
-      <c r="E283" s="9" t="s">
-        <v>540</v>
+      <c r="E283" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F283" t="s">
         <v>492</v>
@@ -18831,8 +18831,8 @@
       <c r="D284">
         <v>2010</v>
       </c>
-      <c r="E284" s="9" t="s">
-        <v>540</v>
+      <c r="E284" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F284" t="s">
         <v>492</v>
@@ -18890,8 +18890,8 @@
       <c r="D285">
         <v>2010</v>
       </c>
-      <c r="E285" s="9" t="s">
-        <v>540</v>
+      <c r="E285" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F285" t="s">
         <v>492</v>
@@ -18949,8 +18949,8 @@
       <c r="D286">
         <v>2010</v>
       </c>
-      <c r="E286" s="9" t="s">
-        <v>540</v>
+      <c r="E286" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F286" t="s">
         <v>492</v>
@@ -19008,8 +19008,8 @@
       <c r="D287">
         <v>2010</v>
       </c>
-      <c r="E287" s="9" t="s">
-        <v>540</v>
+      <c r="E287" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F287" t="s">
         <v>492</v>
@@ -19067,8 +19067,8 @@
       <c r="D288">
         <v>2010</v>
       </c>
-      <c r="E288" s="9" t="s">
-        <v>540</v>
+      <c r="E288" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F288" t="s">
         <v>492</v>
@@ -19126,8 +19126,8 @@
       <c r="D289">
         <v>2010</v>
       </c>
-      <c r="E289" s="9" t="s">
-        <v>540</v>
+      <c r="E289" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F289" t="s">
         <v>492</v>
@@ -19185,8 +19185,8 @@
       <c r="D290">
         <v>2010</v>
       </c>
-      <c r="E290" s="9" t="s">
-        <v>540</v>
+      <c r="E290" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F290" t="s">
         <v>492</v>
@@ -19244,8 +19244,8 @@
       <c r="D291">
         <v>2010</v>
       </c>
-      <c r="E291" s="9" t="s">
-        <v>540</v>
+      <c r="E291" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F291" t="s">
         <v>492</v>
@@ -19303,8 +19303,8 @@
       <c r="D292">
         <v>2010</v>
       </c>
-      <c r="E292" s="9" t="s">
-        <v>540</v>
+      <c r="E292" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F292" t="s">
         <v>492</v>
@@ -19362,8 +19362,8 @@
       <c r="D293">
         <v>2010</v>
       </c>
-      <c r="E293" s="9" t="s">
-        <v>540</v>
+      <c r="E293" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F293" t="s">
         <v>492</v>
@@ -19421,8 +19421,8 @@
       <c r="D294">
         <v>2010</v>
       </c>
-      <c r="E294" s="9" t="s">
-        <v>540</v>
+      <c r="E294" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F294" t="s">
         <v>492</v>
@@ -19480,8 +19480,8 @@
       <c r="D295">
         <v>2010</v>
       </c>
-      <c r="E295" s="9" t="s">
-        <v>540</v>
+      <c r="E295" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F295" t="s">
         <v>492</v>
@@ -19539,8 +19539,8 @@
       <c r="D296">
         <v>2010</v>
       </c>
-      <c r="E296" s="9" t="s">
-        <v>540</v>
+      <c r="E296" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F296" t="s">
         <v>492</v>
@@ -19598,8 +19598,8 @@
       <c r="D297">
         <v>2010</v>
       </c>
-      <c r="E297" s="9" t="s">
-        <v>540</v>
+      <c r="E297" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F297" t="s">
         <v>492</v>
@@ -19657,8 +19657,8 @@
       <c r="D298">
         <v>2010</v>
       </c>
-      <c r="E298" s="9" t="s">
-        <v>540</v>
+      <c r="E298" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F298" t="s">
         <v>492</v>
@@ -19716,8 +19716,8 @@
       <c r="D299">
         <v>2010</v>
       </c>
-      <c r="E299" s="9" t="s">
-        <v>540</v>
+      <c r="E299" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F299" t="s">
         <v>492</v>
@@ -19775,8 +19775,8 @@
       <c r="D300">
         <v>2010</v>
       </c>
-      <c r="E300" s="9" t="s">
-        <v>540</v>
+      <c r="E300" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F300" t="s">
         <v>492</v>
@@ -19834,8 +19834,8 @@
       <c r="D301">
         <v>2010</v>
       </c>
-      <c r="E301" s="9" t="s">
-        <v>540</v>
+      <c r="E301" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F301" t="s">
         <v>492</v>
@@ -19893,8 +19893,8 @@
       <c r="D302">
         <v>2010</v>
       </c>
-      <c r="E302" s="9" t="s">
-        <v>540</v>
+      <c r="E302" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F302" t="s">
         <v>492</v>
@@ -19952,8 +19952,8 @@
       <c r="D303">
         <v>2010</v>
       </c>
-      <c r="E303" s="9" t="s">
-        <v>540</v>
+      <c r="E303" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F303" t="s">
         <v>492</v>
@@ -20011,8 +20011,8 @@
       <c r="D304">
         <v>2010</v>
       </c>
-      <c r="E304" s="9" t="s">
-        <v>540</v>
+      <c r="E304" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F304" t="s">
         <v>492</v>
@@ -20070,8 +20070,8 @@
       <c r="D305">
         <v>2010</v>
       </c>
-      <c r="E305" s="9" t="s">
-        <v>540</v>
+      <c r="E305" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F305" t="s">
         <v>492</v>
@@ -20129,8 +20129,8 @@
       <c r="D306">
         <v>2010</v>
       </c>
-      <c r="E306" s="9" t="s">
-        <v>540</v>
+      <c r="E306" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F306" t="s">
         <v>492</v>
@@ -20188,8 +20188,8 @@
       <c r="D307">
         <v>2010</v>
       </c>
-      <c r="E307" s="9" t="s">
-        <v>540</v>
+      <c r="E307" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F307" t="s">
         <v>491</v>
@@ -20247,8 +20247,8 @@
       <c r="D308">
         <v>2010</v>
       </c>
-      <c r="E308" s="9" t="s">
-        <v>540</v>
+      <c r="E308" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F308" t="s">
         <v>491</v>
@@ -20306,8 +20306,8 @@
       <c r="D309">
         <v>2010</v>
       </c>
-      <c r="E309" s="9" t="s">
-        <v>540</v>
+      <c r="E309" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F309" t="s">
         <v>491</v>
@@ -20365,8 +20365,8 @@
       <c r="D310">
         <v>2010</v>
       </c>
-      <c r="E310" s="9" t="s">
-        <v>540</v>
+      <c r="E310" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F310" t="s">
         <v>491</v>
@@ -20424,8 +20424,8 @@
       <c r="D311">
         <v>2010</v>
       </c>
-      <c r="E311" s="9" t="s">
-        <v>540</v>
+      <c r="E311" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F311" t="s">
         <v>491</v>
@@ -20483,8 +20483,8 @@
       <c r="D312">
         <v>2010</v>
       </c>
-      <c r="E312" s="9" t="s">
-        <v>540</v>
+      <c r="E312" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F312" t="s">
         <v>491</v>
@@ -20542,8 +20542,8 @@
       <c r="D313">
         <v>2010</v>
       </c>
-      <c r="E313" s="9" t="s">
-        <v>540</v>
+      <c r="E313" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F313" t="s">
         <v>491</v>
@@ -20601,8 +20601,8 @@
       <c r="D314">
         <v>2010</v>
       </c>
-      <c r="E314" s="9" t="s">
-        <v>540</v>
+      <c r="E314" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F314" t="s">
         <v>491</v>
@@ -20660,8 +20660,8 @@
       <c r="D315">
         <v>2010</v>
       </c>
-      <c r="E315" s="9" t="s">
-        <v>540</v>
+      <c r="E315" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F315" t="s">
         <v>491</v>
@@ -20719,8 +20719,8 @@
       <c r="D316">
         <v>2010</v>
       </c>
-      <c r="E316" s="9" t="s">
-        <v>540</v>
+      <c r="E316" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F316" t="s">
         <v>491</v>
@@ -20778,8 +20778,8 @@
       <c r="D317">
         <v>2010</v>
       </c>
-      <c r="E317" s="9" t="s">
-        <v>540</v>
+      <c r="E317" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F317" t="s">
         <v>491</v>
@@ -20837,8 +20837,8 @@
       <c r="D318">
         <v>2010</v>
       </c>
-      <c r="E318" s="9" t="s">
-        <v>540</v>
+      <c r="E318" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F318" t="s">
         <v>491</v>
@@ -20896,8 +20896,8 @@
       <c r="D319">
         <v>2010</v>
       </c>
-      <c r="E319" s="9" t="s">
-        <v>540</v>
+      <c r="E319" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F319" t="s">
         <v>491</v>
@@ -20955,8 +20955,8 @@
       <c r="D320">
         <v>2010</v>
       </c>
-      <c r="E320" s="9" t="s">
-        <v>540</v>
+      <c r="E320" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F320" t="s">
         <v>491</v>
@@ -21014,8 +21014,8 @@
       <c r="D321">
         <v>2010</v>
       </c>
-      <c r="E321" s="9" t="s">
-        <v>540</v>
+      <c r="E321" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F321" t="s">
         <v>491</v>
@@ -21073,8 +21073,8 @@
       <c r="D322">
         <v>2010</v>
       </c>
-      <c r="E322" s="9" t="s">
-        <v>540</v>
+      <c r="E322" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F322" t="s">
         <v>492</v>
@@ -21132,8 +21132,8 @@
       <c r="D323">
         <v>2010</v>
       </c>
-      <c r="E323" s="9" t="s">
-        <v>540</v>
+      <c r="E323" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F323" t="s">
         <v>492</v>
@@ -21191,8 +21191,8 @@
       <c r="D324">
         <v>2010</v>
       </c>
-      <c r="E324" s="9" t="s">
-        <v>540</v>
+      <c r="E324" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F324" t="s">
         <v>492</v>
@@ -21250,8 +21250,8 @@
       <c r="D325">
         <v>2010</v>
       </c>
-      <c r="E325" s="9" t="s">
-        <v>540</v>
+      <c r="E325" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F325" t="s">
         <v>492</v>
@@ -21309,8 +21309,8 @@
       <c r="D326">
         <v>2010</v>
       </c>
-      <c r="E326" s="9" t="s">
-        <v>540</v>
+      <c r="E326" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F326" t="s">
         <v>492</v>
@@ -21368,8 +21368,8 @@
       <c r="D327">
         <v>2010</v>
       </c>
-      <c r="E327" s="9" t="s">
-        <v>540</v>
+      <c r="E327" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F327" t="s">
         <v>492</v>
@@ -21427,8 +21427,8 @@
       <c r="D328">
         <v>2010</v>
       </c>
-      <c r="E328" s="9" t="s">
-        <v>540</v>
+      <c r="E328" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F328" t="s">
         <v>492</v>
@@ -21486,8 +21486,8 @@
       <c r="D329">
         <v>2010</v>
       </c>
-      <c r="E329" s="9" t="s">
-        <v>540</v>
+      <c r="E329" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F329" t="s">
         <v>492</v>
@@ -21545,8 +21545,8 @@
       <c r="D330">
         <v>2010</v>
       </c>
-      <c r="E330" s="9" t="s">
-        <v>540</v>
+      <c r="E330" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F330" t="s">
         <v>492</v>
@@ -21604,8 +21604,8 @@
       <c r="D331">
         <v>2010</v>
       </c>
-      <c r="E331" s="9" t="s">
-        <v>540</v>
+      <c r="E331" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F331" t="s">
         <v>492</v>
@@ -21663,8 +21663,8 @@
       <c r="D332">
         <v>2010</v>
       </c>
-      <c r="E332" s="9" t="s">
-        <v>540</v>
+      <c r="E332" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F332" t="s">
         <v>492</v>
@@ -21722,8 +21722,8 @@
       <c r="D333">
         <v>2010</v>
       </c>
-      <c r="E333" s="9" t="s">
-        <v>540</v>
+      <c r="E333" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F333" t="s">
         <v>492</v>
@@ -21781,8 +21781,8 @@
       <c r="D334">
         <v>2010</v>
       </c>
-      <c r="E334" s="9" t="s">
-        <v>540</v>
+      <c r="E334" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F334" t="s">
         <v>492</v>
@@ -21840,8 +21840,8 @@
       <c r="D335">
         <v>2010</v>
       </c>
-      <c r="E335" s="9" t="s">
-        <v>540</v>
+      <c r="E335" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F335" t="s">
         <v>492</v>
@@ -21899,8 +21899,8 @@
       <c r="D336">
         <v>2010</v>
       </c>
-      <c r="E336" s="9" t="s">
-        <v>540</v>
+      <c r="E336" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F336" t="s">
         <v>492</v>
@@ -21958,8 +21958,8 @@
       <c r="D337">
         <v>2010</v>
       </c>
-      <c r="E337" s="9" t="s">
-        <v>540</v>
+      <c r="E337" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F337" t="s">
         <v>492</v>
@@ -22017,8 +22017,8 @@
       <c r="D338">
         <v>2010</v>
       </c>
-      <c r="E338" s="9" t="s">
-        <v>540</v>
+      <c r="E338" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F338" t="s">
         <v>492</v>
@@ -22076,8 +22076,8 @@
       <c r="D339">
         <v>2010</v>
       </c>
-      <c r="E339" s="9" t="s">
-        <v>540</v>
+      <c r="E339" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F339" t="s">
         <v>492</v>
@@ -22135,8 +22135,8 @@
       <c r="D340">
         <v>2010</v>
       </c>
-      <c r="E340" s="9" t="s">
-        <v>540</v>
+      <c r="E340" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F340" t="s">
         <v>492</v>
@@ -22194,8 +22194,8 @@
       <c r="D341">
         <v>2010</v>
       </c>
-      <c r="E341" s="9" t="s">
-        <v>540</v>
+      <c r="E341" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F341" t="s">
         <v>492</v>
@@ -22253,8 +22253,8 @@
       <c r="D342">
         <v>2010</v>
       </c>
-      <c r="E342" s="9" t="s">
-        <v>540</v>
+      <c r="E342" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F342" t="s">
         <v>492</v>
@@ -22312,8 +22312,8 @@
       <c r="D343">
         <v>2010</v>
       </c>
-      <c r="E343" s="9" t="s">
-        <v>540</v>
+      <c r="E343" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F343" t="s">
         <v>491</v>
@@ -22371,8 +22371,8 @@
       <c r="D344">
         <v>2010</v>
       </c>
-      <c r="E344" s="9" t="s">
-        <v>540</v>
+      <c r="E344" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F344" t="s">
         <v>491</v>
@@ -22430,8 +22430,8 @@
       <c r="D345">
         <v>2010</v>
       </c>
-      <c r="E345" s="9" t="s">
-        <v>540</v>
+      <c r="E345" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F345" t="s">
         <v>491</v>
@@ -22489,8 +22489,8 @@
       <c r="D346">
         <v>2010</v>
       </c>
-      <c r="E346" s="9" t="s">
-        <v>540</v>
+      <c r="E346" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F346" t="s">
         <v>491</v>
@@ -22548,8 +22548,8 @@
       <c r="D347">
         <v>2010</v>
       </c>
-      <c r="E347" s="9" t="s">
-        <v>540</v>
+      <c r="E347" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F347" t="s">
         <v>491</v>
@@ -22607,8 +22607,8 @@
       <c r="D348">
         <v>2010</v>
       </c>
-      <c r="E348" s="9" t="s">
-        <v>540</v>
+      <c r="E348" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F348" t="s">
         <v>491</v>
@@ -22666,8 +22666,8 @@
       <c r="D349">
         <v>2010</v>
       </c>
-      <c r="E349" s="9" t="s">
-        <v>540</v>
+      <c r="E349" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F349" t="s">
         <v>491</v>
@@ -22725,8 +22725,8 @@
       <c r="D350">
         <v>2010</v>
       </c>
-      <c r="E350" s="9" t="s">
-        <v>540</v>
+      <c r="E350" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F350" t="s">
         <v>491</v>
@@ -22784,8 +22784,8 @@
       <c r="D351">
         <v>2010</v>
       </c>
-      <c r="E351" s="9" t="s">
-        <v>540</v>
+      <c r="E351" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F351" t="s">
         <v>491</v>
@@ -22843,8 +22843,8 @@
       <c r="D352">
         <v>2010</v>
       </c>
-      <c r="E352" s="9" t="s">
-        <v>540</v>
+      <c r="E352" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F352" t="s">
         <v>491</v>
@@ -22902,8 +22902,8 @@
       <c r="D353">
         <v>2010</v>
       </c>
-      <c r="E353" s="9" t="s">
-        <v>540</v>
+      <c r="E353" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F353" t="s">
         <v>491</v>
@@ -22961,8 +22961,8 @@
       <c r="D354">
         <v>2010</v>
       </c>
-      <c r="E354" s="9" t="s">
-        <v>540</v>
+      <c r="E354" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F354" t="s">
         <v>491</v>
@@ -23020,8 +23020,8 @@
       <c r="D355">
         <v>2010</v>
       </c>
-      <c r="E355" s="9" t="s">
-        <v>540</v>
+      <c r="E355" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F355" t="s">
         <v>491</v>
@@ -23079,8 +23079,8 @@
       <c r="D356">
         <v>2010</v>
       </c>
-      <c r="E356" s="9" t="s">
-        <v>540</v>
+      <c r="E356" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F356" t="s">
         <v>491</v>
@@ -23138,8 +23138,8 @@
       <c r="D357">
         <v>2010</v>
       </c>
-      <c r="E357" s="9" t="s">
-        <v>540</v>
+      <c r="E357" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F357" t="s">
         <v>491</v>
@@ -23197,8 +23197,8 @@
       <c r="D358">
         <v>2010</v>
       </c>
-      <c r="E358" s="9" t="s">
-        <v>540</v>
+      <c r="E358" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F358" t="s">
         <v>491</v>
@@ -23256,8 +23256,8 @@
       <c r="D359">
         <v>2010</v>
       </c>
-      <c r="E359" s="9" t="s">
-        <v>540</v>
+      <c r="E359" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F359" t="s">
         <v>491</v>
@@ -23315,8 +23315,8 @@
       <c r="D360">
         <v>2010</v>
       </c>
-      <c r="E360" s="9" t="s">
-        <v>540</v>
+      <c r="E360" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F360" t="s">
         <v>491</v>
@@ -23374,8 +23374,8 @@
       <c r="D361">
         <v>2010</v>
       </c>
-      <c r="E361" s="9" t="s">
-        <v>540</v>
+      <c r="E361" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F361" t="s">
         <v>491</v>
@@ -23433,8 +23433,8 @@
       <c r="D362">
         <v>2010</v>
       </c>
-      <c r="E362" s="9" t="s">
-        <v>540</v>
+      <c r="E362" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F362" t="s">
         <v>491</v>
@@ -23492,8 +23492,8 @@
       <c r="D363">
         <v>2010</v>
       </c>
-      <c r="E363" s="9" t="s">
-        <v>540</v>
+      <c r="E363" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F363" t="s">
         <v>492</v>
@@ -23551,8 +23551,8 @@
       <c r="D364">
         <v>2010</v>
       </c>
-      <c r="E364" s="9" t="s">
-        <v>540</v>
+      <c r="E364" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F364" t="s">
         <v>492</v>
@@ -23610,8 +23610,8 @@
       <c r="D365">
         <v>2010</v>
       </c>
-      <c r="E365" s="9" t="s">
-        <v>540</v>
+      <c r="E365" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F365" t="s">
         <v>491</v>
@@ -23669,8 +23669,8 @@
       <c r="D366">
         <v>2010</v>
       </c>
-      <c r="E366" s="9" t="s">
-        <v>540</v>
+      <c r="E366" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F366" t="s">
         <v>491</v>
@@ -23728,8 +23728,8 @@
       <c r="D367">
         <v>2010</v>
       </c>
-      <c r="E367" s="9" t="s">
-        <v>540</v>
+      <c r="E367" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F367" t="s">
         <v>491</v>
@@ -23787,8 +23787,8 @@
       <c r="D368">
         <v>2010</v>
       </c>
-      <c r="E368" s="9" t="s">
-        <v>540</v>
+      <c r="E368" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F368" t="s">
         <v>491</v>
@@ -23846,8 +23846,8 @@
       <c r="D369">
         <v>2010</v>
       </c>
-      <c r="E369" s="9" t="s">
-        <v>540</v>
+      <c r="E369" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F369" t="s">
         <v>491</v>
@@ -23905,8 +23905,8 @@
       <c r="D370">
         <v>2010</v>
       </c>
-      <c r="E370" s="9" t="s">
-        <v>540</v>
+      <c r="E370" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F370" t="s">
         <v>491</v>
@@ -23964,8 +23964,8 @@
       <c r="D371">
         <v>2010</v>
       </c>
-      <c r="E371" s="9" t="s">
-        <v>540</v>
+      <c r="E371" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F371" t="s">
         <v>491</v>
@@ -24023,8 +24023,8 @@
       <c r="D372">
         <v>2010</v>
       </c>
-      <c r="E372" s="9" t="s">
-        <v>540</v>
+      <c r="E372" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F372" t="s">
         <v>491</v>
@@ -24082,8 +24082,8 @@
       <c r="D373">
         <v>2010</v>
       </c>
-      <c r="E373" s="9" t="s">
-        <v>540</v>
+      <c r="E373" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F373" t="s">
         <v>491</v>
@@ -24141,8 +24141,8 @@
       <c r="D374">
         <v>2010</v>
       </c>
-      <c r="E374" s="9" t="s">
-        <v>540</v>
+      <c r="E374" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F374" t="s">
         <v>491</v>
@@ -24200,8 +24200,8 @@
       <c r="D375">
         <v>2010</v>
       </c>
-      <c r="E375" s="9" t="s">
-        <v>540</v>
+      <c r="E375" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F375" t="s">
         <v>491</v>
@@ -24259,8 +24259,8 @@
       <c r="D376">
         <v>2010</v>
       </c>
-      <c r="E376" s="9" t="s">
-        <v>540</v>
+      <c r="E376" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F376" t="s">
         <v>491</v>
@@ -24318,8 +24318,8 @@
       <c r="D377">
         <v>2010</v>
       </c>
-      <c r="E377" s="9" t="s">
-        <v>540</v>
+      <c r="E377" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F377" t="s">
         <v>492</v>
@@ -24377,8 +24377,8 @@
       <c r="D378">
         <v>2010</v>
       </c>
-      <c r="E378" s="9" t="s">
-        <v>540</v>
+      <c r="E378" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F378" t="s">
         <v>492</v>
@@ -24436,8 +24436,8 @@
       <c r="D379">
         <v>2010</v>
       </c>
-      <c r="E379" s="9" t="s">
-        <v>540</v>
+      <c r="E379" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F379" t="s">
         <v>492</v>
@@ -24495,8 +24495,8 @@
       <c r="D380">
         <v>2010</v>
       </c>
-      <c r="E380" s="9" t="s">
-        <v>540</v>
+      <c r="E380" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F380" t="s">
         <v>492</v>
@@ -24554,8 +24554,8 @@
       <c r="D381">
         <v>2010</v>
       </c>
-      <c r="E381" s="9" t="s">
-        <v>540</v>
+      <c r="E381" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F381" t="s">
         <v>492</v>
@@ -24613,8 +24613,8 @@
       <c r="D382">
         <v>2010</v>
       </c>
-      <c r="E382" s="9" t="s">
-        <v>540</v>
+      <c r="E382" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F382" t="s">
         <v>492</v>
@@ -24672,8 +24672,8 @@
       <c r="D383">
         <v>2010</v>
       </c>
-      <c r="E383" s="9" t="s">
-        <v>540</v>
+      <c r="E383" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F383" t="s">
         <v>492</v>
@@ -24731,8 +24731,8 @@
       <c r="D384">
         <v>2010</v>
       </c>
-      <c r="E384" s="9" t="s">
-        <v>540</v>
+      <c r="E384" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F384" t="s">
         <v>492</v>
@@ -24790,8 +24790,8 @@
       <c r="D385">
         <v>2010</v>
       </c>
-      <c r="E385" s="9" t="s">
-        <v>540</v>
+      <c r="E385" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F385" t="s">
         <v>492</v>
@@ -24849,8 +24849,8 @@
       <c r="D386">
         <v>2010</v>
       </c>
-      <c r="E386" s="9" t="s">
-        <v>540</v>
+      <c r="E386" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F386" t="s">
         <v>492</v>
@@ -24908,8 +24908,8 @@
       <c r="D387">
         <v>2010</v>
       </c>
-      <c r="E387" s="9" t="s">
-        <v>540</v>
+      <c r="E387" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F387" t="s">
         <v>492</v>
@@ -24967,8 +24967,8 @@
       <c r="D388">
         <v>2010</v>
       </c>
-      <c r="E388" s="9" t="s">
-        <v>540</v>
+      <c r="E388" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F388" t="s">
         <v>492</v>
@@ -25026,8 +25026,8 @@
       <c r="D389">
         <v>2010</v>
       </c>
-      <c r="E389" s="9" t="s">
-        <v>540</v>
+      <c r="E389" s="10" t="s">
+        <v>493</v>
       </c>
       <c r="F389" t="s">
         <v>492</v>
@@ -25085,8 +25085,8 @@
       <c r="D390">
         <v>2006</v>
       </c>
-      <c r="E390" s="10" t="s">
-        <v>493</v>
+      <c r="E390" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G390">
         <v>50.215499999999999</v>
@@ -25138,8 +25138,8 @@
       <c r="D391">
         <v>2006</v>
       </c>
-      <c r="E391" s="10" t="s">
-        <v>493</v>
+      <c r="E391" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G391">
         <v>53.144500000000001</v>
@@ -25191,8 +25191,8 @@
       <c r="D392">
         <v>2006</v>
       </c>
-      <c r="E392" s="10" t="s">
-        <v>493</v>
+      <c r="E392" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G392">
         <v>52.321399999999997</v>
@@ -25244,8 +25244,8 @@
       <c r="D393">
         <v>2006</v>
       </c>
-      <c r="E393" s="10" t="s">
-        <v>493</v>
+      <c r="E393" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G393">
         <v>52.1509</v>
@@ -25297,8 +25297,8 @@
       <c r="D394">
         <v>2006</v>
       </c>
-      <c r="E394" s="10" t="s">
-        <v>493</v>
+      <c r="E394" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G394">
         <v>50.286900000000003</v>
@@ -25350,8 +25350,8 @@
       <c r="D395">
         <v>2006</v>
       </c>
-      <c r="E395" s="10" t="s">
-        <v>493</v>
+      <c r="E395" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G395">
         <v>50.713700000000003</v>
@@ -25403,8 +25403,8 @@
       <c r="D396">
         <v>2006</v>
       </c>
-      <c r="E396" s="10" t="s">
-        <v>493</v>
+      <c r="E396" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G396">
         <v>52.264400000000002</v>
@@ -25456,8 +25456,8 @@
       <c r="D397">
         <v>2006</v>
       </c>
-      <c r="E397" s="10" t="s">
-        <v>493</v>
+      <c r="E397" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G397">
         <v>51.719200000000001</v>
@@ -25509,8 +25509,8 @@
       <c r="D398">
         <v>2006</v>
       </c>
-      <c r="E398" s="10" t="s">
-        <v>493</v>
+      <c r="E398" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G398">
         <v>51.429099999999998</v>
@@ -25562,8 +25562,8 @@
       <c r="D399">
         <v>2006</v>
       </c>
-      <c r="E399" s="10" t="s">
-        <v>493</v>
+      <c r="E399" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G399">
         <v>51.997500000000002</v>
@@ -25615,8 +25615,8 @@
       <c r="D400">
         <v>2006</v>
       </c>
-      <c r="E400" s="10" t="s">
-        <v>493</v>
+      <c r="E400" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G400">
         <v>51.853000000000002</v>
@@ -25668,8 +25668,8 @@
       <c r="D401">
         <v>2006</v>
       </c>
-      <c r="E401" s="10" t="s">
-        <v>493</v>
+      <c r="E401" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G401">
         <v>52.081499999999998</v>
@@ -25721,8 +25721,8 @@
       <c r="D402">
         <v>2006</v>
       </c>
-      <c r="E402" s="10" t="s">
-        <v>493</v>
+      <c r="E402" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G402">
         <v>51.983800000000002</v>
@@ -25774,8 +25774,8 @@
       <c r="D403">
         <v>2006</v>
       </c>
-      <c r="E403" s="10" t="s">
-        <v>493</v>
+      <c r="E403" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F403" t="s">
         <v>491</v>
@@ -25830,8 +25830,8 @@
       <c r="D404">
         <v>2006</v>
       </c>
-      <c r="E404" s="10" t="s">
-        <v>493</v>
+      <c r="E404" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F404" t="s">
         <v>491</v>
@@ -25886,8 +25886,8 @@
       <c r="D405">
         <v>2006</v>
       </c>
-      <c r="E405" s="10" t="s">
-        <v>493</v>
+      <c r="E405" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G405">
         <v>50.154499999999999</v>
@@ -25939,8 +25939,8 @@
       <c r="D406">
         <v>2006</v>
       </c>
-      <c r="E406" s="10" t="s">
-        <v>493</v>
+      <c r="E406" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G406">
         <v>50.802100000000003</v>
@@ -25992,8 +25992,8 @@
       <c r="D407">
         <v>2006</v>
       </c>
-      <c r="E407" s="10" t="s">
-        <v>493</v>
+      <c r="E407" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G407">
         <v>51.566000000000003</v>
@@ -26045,8 +26045,8 @@
       <c r="D408">
         <v>2006</v>
       </c>
-      <c r="E408" s="10" t="s">
-        <v>493</v>
+      <c r="E408" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G408">
         <v>50.564700000000002</v>
@@ -26098,8 +26098,8 @@
       <c r="D409">
         <v>2006</v>
       </c>
-      <c r="E409" s="10" t="s">
-        <v>493</v>
+      <c r="E409" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G409">
         <v>51.479599999999998</v>
@@ -26151,8 +26151,8 @@
       <c r="D410">
         <v>2006</v>
       </c>
-      <c r="E410" s="10" t="s">
-        <v>493</v>
+      <c r="E410" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G410">
         <v>51.427300000000002</v>
@@ -26204,8 +26204,8 @@
       <c r="D411">
         <v>2006</v>
       </c>
-      <c r="E411" s="10" t="s">
-        <v>493</v>
+      <c r="E411" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G411">
         <v>50.897300000000001</v>
@@ -26257,8 +26257,8 @@
       <c r="D412">
         <v>2006</v>
       </c>
-      <c r="E412" s="10" t="s">
-        <v>493</v>
+      <c r="E412" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G412">
         <v>51.141500000000001</v>
@@ -26310,8 +26310,8 @@
       <c r="D413">
         <v>2006</v>
       </c>
-      <c r="E413" s="10" t="s">
-        <v>493</v>
+      <c r="E413" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G413">
         <v>51.336100000000002</v>
@@ -26363,8 +26363,8 @@
       <c r="D414">
         <v>2006</v>
       </c>
-      <c r="E414" s="10" t="s">
-        <v>493</v>
+      <c r="E414" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G414">
         <v>51.109099999999998</v>
@@ -26416,8 +26416,8 @@
       <c r="D415">
         <v>2006</v>
       </c>
-      <c r="E415" s="10" t="s">
-        <v>493</v>
+      <c r="E415" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F415" t="s">
         <v>491</v>
@@ -26472,8 +26472,8 @@
       <c r="D416">
         <v>2006</v>
       </c>
-      <c r="E416" s="10" t="s">
-        <v>493</v>
+      <c r="E416" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F416" t="s">
         <v>492</v>
@@ -26528,8 +26528,8 @@
       <c r="D417">
         <v>2006</v>
       </c>
-      <c r="E417" s="10" t="s">
-        <v>493</v>
+      <c r="E417" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F417" t="s">
         <v>492</v>
@@ -26584,8 +26584,8 @@
       <c r="D418">
         <v>2006</v>
       </c>
-      <c r="E418" s="10" t="s">
-        <v>493</v>
+      <c r="E418" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F418" t="s">
         <v>491</v>
@@ -26640,8 +26640,8 @@
       <c r="D419">
         <v>2006</v>
       </c>
-      <c r="E419" s="10" t="s">
-        <v>493</v>
+      <c r="E419" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F419" t="s">
         <v>492</v>
@@ -26696,8 +26696,8 @@
       <c r="D420">
         <v>2006</v>
       </c>
-      <c r="E420" s="10" t="s">
-        <v>493</v>
+      <c r="E420" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F420" t="s">
         <v>491</v>
@@ -26752,8 +26752,8 @@
       <c r="D421">
         <v>2006</v>
       </c>
-      <c r="E421" s="10" t="s">
-        <v>493</v>
+      <c r="E421" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F421" t="s">
         <v>492</v>
@@ -26808,8 +26808,8 @@
       <c r="D422">
         <v>2006</v>
       </c>
-      <c r="E422" s="10" t="s">
-        <v>493</v>
+      <c r="E422" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F422" t="s">
         <v>492</v>
@@ -26864,8 +26864,8 @@
       <c r="D423">
         <v>2006</v>
       </c>
-      <c r="E423" s="10" t="s">
-        <v>493</v>
+      <c r="E423" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G423">
         <v>51.210299999999997</v>
@@ -26917,8 +26917,8 @@
       <c r="D424">
         <v>2006</v>
       </c>
-      <c r="E424" s="10" t="s">
-        <v>493</v>
+      <c r="E424" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G424">
         <v>50.904800000000002</v>
@@ -26970,8 +26970,8 @@
       <c r="D425">
         <v>2010</v>
       </c>
-      <c r="E425" s="10" t="s">
-        <v>493</v>
+      <c r="E425" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F425" t="s">
         <v>492</v>
@@ -27026,8 +27026,8 @@
       <c r="D426">
         <v>2010</v>
       </c>
-      <c r="E426" s="10" t="s">
-        <v>493</v>
+      <c r="E426" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G426">
         <v>51.6295</v>
@@ -27079,8 +27079,8 @@
       <c r="D427">
         <v>2010</v>
       </c>
-      <c r="E427" s="10" t="s">
-        <v>493</v>
+      <c r="E427" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G427">
         <v>51.912100000000002</v>
@@ -27132,8 +27132,8 @@
       <c r="D428">
         <v>2010</v>
       </c>
-      <c r="E428" s="10" t="s">
-        <v>493</v>
+      <c r="E428" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F428" t="s">
         <v>492</v>
@@ -27188,8 +27188,8 @@
       <c r="D429">
         <v>2010</v>
       </c>
-      <c r="E429" s="10" t="s">
-        <v>493</v>
+      <c r="E429" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F429" t="s">
         <v>492</v>
@@ -27244,8 +27244,8 @@
       <c r="D430">
         <v>2010</v>
       </c>
-      <c r="E430" s="10" t="s">
-        <v>493</v>
+      <c r="E430" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G430">
         <v>48.392299999999999</v>
@@ -27297,8 +27297,8 @@
       <c r="D431">
         <v>2010</v>
       </c>
-      <c r="E431" s="10" t="s">
-        <v>493</v>
+      <c r="E431" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G431">
         <v>46.825200000000002</v>
@@ -27350,8 +27350,8 @@
       <c r="D432">
         <v>2010</v>
       </c>
-      <c r="E432" s="10" t="s">
-        <v>493</v>
+      <c r="E432" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G432">
         <v>47.657699999999998</v>
@@ -27403,8 +27403,8 @@
       <c r="D433">
         <v>2010</v>
       </c>
-      <c r="E433" s="10" t="s">
-        <v>493</v>
+      <c r="E433" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F433" t="s">
         <v>492</v>
@@ -27459,8 +27459,8 @@
       <c r="D434">
         <v>2010</v>
       </c>
-      <c r="E434" s="10" t="s">
-        <v>493</v>
+      <c r="E434" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F434" t="s">
         <v>492</v>
@@ -27515,8 +27515,8 @@
       <c r="D435">
         <v>2010</v>
       </c>
-      <c r="E435" s="10" t="s">
-        <v>493</v>
+      <c r="E435" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F435" t="s">
         <v>492</v>
@@ -27571,8 +27571,8 @@
       <c r="D436">
         <v>2010</v>
       </c>
-      <c r="E436" s="10" t="s">
-        <v>493</v>
+      <c r="E436" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G436">
         <v>47.965600000000002</v>
@@ -27624,8 +27624,8 @@
       <c r="D437">
         <v>2010</v>
       </c>
-      <c r="E437" s="10" t="s">
-        <v>493</v>
+      <c r="E437" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G437">
         <v>46.962499999999999</v>
@@ -27677,8 +27677,8 @@
       <c r="D438">
         <v>2010</v>
       </c>
-      <c r="E438" s="10" t="s">
-        <v>493</v>
+      <c r="E438" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G438">
         <v>46.741100000000003</v>
@@ -27730,8 +27730,8 @@
       <c r="D439">
         <v>2010</v>
       </c>
-      <c r="E439" s="10" t="s">
-        <v>493</v>
+      <c r="E439" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G439">
         <v>45.429000000000002</v>
@@ -27783,8 +27783,8 @@
       <c r="D440">
         <v>2010</v>
       </c>
-      <c r="E440" s="10" t="s">
-        <v>493</v>
+      <c r="E440" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F440" t="s">
         <v>491</v>
@@ -27839,8 +27839,8 @@
       <c r="D441">
         <v>2010</v>
       </c>
-      <c r="E441" s="10" t="s">
-        <v>493</v>
+      <c r="E441" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F441" t="s">
         <v>492</v>
@@ -27895,8 +27895,8 @@
       <c r="D442">
         <v>2010</v>
       </c>
-      <c r="E442" s="10" t="s">
-        <v>493</v>
+      <c r="E442" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F442" t="s">
         <v>492</v>
@@ -27951,8 +27951,8 @@
       <c r="D443">
         <v>2010</v>
       </c>
-      <c r="E443" s="10" t="s">
-        <v>493</v>
+      <c r="E443" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F443" t="s">
         <v>491</v>
@@ -28007,8 +28007,8 @@
       <c r="D444">
         <v>2010</v>
       </c>
-      <c r="E444" s="10" t="s">
-        <v>493</v>
+      <c r="E444" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G444">
         <v>50.271000000000001</v>
@@ -28060,8 +28060,8 @@
       <c r="D445">
         <v>2010</v>
       </c>
-      <c r="E445" s="10" t="s">
-        <v>493</v>
+      <c r="E445" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G445">
         <v>48.354999999999997</v>
@@ -28113,8 +28113,8 @@
       <c r="D446">
         <v>2010</v>
       </c>
-      <c r="E446" s="10" t="s">
-        <v>493</v>
+      <c r="E446" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G446">
         <v>50.6494</v>
@@ -28166,8 +28166,8 @@
       <c r="D447">
         <v>2010</v>
       </c>
-      <c r="E447" s="10" t="s">
-        <v>493</v>
+      <c r="E447" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G447">
         <v>51.224600000000002</v>
@@ -28219,8 +28219,8 @@
       <c r="D448">
         <v>2010</v>
       </c>
-      <c r="E448" s="10" t="s">
-        <v>493</v>
+      <c r="E448" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G448">
         <v>52.441699999999997</v>
@@ -28272,8 +28272,8 @@
       <c r="D449">
         <v>2010</v>
       </c>
-      <c r="E449" s="10" t="s">
-        <v>493</v>
+      <c r="E449" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G449">
         <v>47.673200000000001</v>
@@ -28325,8 +28325,8 @@
       <c r="D450">
         <v>2010</v>
       </c>
-      <c r="E450" s="10" t="s">
-        <v>493</v>
+      <c r="E450" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G450">
         <v>52.6267</v>
@@ -28378,8 +28378,8 @@
       <c r="D451">
         <v>2010</v>
       </c>
-      <c r="E451" s="10" t="s">
-        <v>493</v>
+      <c r="E451" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G451">
         <v>51.896599999999999</v>
@@ -28431,8 +28431,8 @@
       <c r="D452">
         <v>2010</v>
       </c>
-      <c r="E452" s="10" t="s">
-        <v>493</v>
+      <c r="E452" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G452">
         <v>50.389299999999999</v>
@@ -28484,8 +28484,8 @@
       <c r="D453">
         <v>2010</v>
       </c>
-      <c r="E453" s="10" t="s">
-        <v>493</v>
+      <c r="E453" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G453">
         <v>52.139200000000002</v>
@@ -28537,8 +28537,8 @@
       <c r="D454">
         <v>2010</v>
       </c>
-      <c r="E454" s="10" t="s">
-        <v>493</v>
+      <c r="E454" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G454">
         <v>51.399799999999999</v>
@@ -28590,8 +28590,8 @@
       <c r="D455">
         <v>2010</v>
       </c>
-      <c r="E455" s="10" t="s">
-        <v>493</v>
+      <c r="E455" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G455">
         <v>49.427</v>
@@ -28643,8 +28643,8 @@
       <c r="D456">
         <v>2010</v>
       </c>
-      <c r="E456" s="10" t="s">
-        <v>493</v>
+      <c r="E456" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G456">
         <v>51.782400000000003</v>
@@ -28696,8 +28696,8 @@
       <c r="D457">
         <v>2010</v>
       </c>
-      <c r="E457" s="10" t="s">
-        <v>493</v>
+      <c r="E457" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F457" t="s">
         <v>491</v>
@@ -28752,8 +28752,8 @@
       <c r="D458">
         <v>2010</v>
       </c>
-      <c r="E458" s="10" t="s">
-        <v>493</v>
+      <c r="E458" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G458">
         <v>50.922699999999999</v>
@@ -28805,8 +28805,8 @@
       <c r="D459">
         <v>2010</v>
       </c>
-      <c r="E459" s="10" t="s">
-        <v>493</v>
+      <c r="E459" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G459">
         <v>52.1447</v>
@@ -28858,8 +28858,8 @@
       <c r="D460">
         <v>2010</v>
       </c>
-      <c r="E460" s="10" t="s">
-        <v>493</v>
+      <c r="E460" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F460" t="s">
         <v>492</v>
@@ -28914,8 +28914,8 @@
       <c r="D461">
         <v>2010</v>
       </c>
-      <c r="E461" s="10" t="s">
-        <v>493</v>
+      <c r="E461" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F461" t="s">
         <v>491</v>
@@ -28970,8 +28970,8 @@
       <c r="D462">
         <v>2010</v>
       </c>
-      <c r="E462" s="10" t="s">
-        <v>493</v>
+      <c r="E462" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F462" t="s">
         <v>491</v>
@@ -29026,8 +29026,8 @@
       <c r="D463">
         <v>2010</v>
       </c>
-      <c r="E463" s="10" t="s">
-        <v>493</v>
+      <c r="E463" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F463" t="s">
         <v>491</v>
@@ -29082,8 +29082,8 @@
       <c r="D464">
         <v>2010</v>
       </c>
-      <c r="E464" s="10" t="s">
-        <v>493</v>
+      <c r="E464" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G464">
         <v>51.855899999999998</v>
@@ -29135,8 +29135,8 @@
       <c r="D465">
         <v>2010</v>
       </c>
-      <c r="E465" s="10" t="s">
-        <v>493</v>
+      <c r="E465" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G465">
         <v>51.496000000000002</v>
@@ -29188,8 +29188,8 @@
       <c r="D466">
         <v>2010</v>
       </c>
-      <c r="E466" s="10" t="s">
-        <v>493</v>
+      <c r="E466" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G466">
         <v>51.464300000000001</v>
@@ -29241,8 +29241,8 @@
       <c r="D467">
         <v>2010</v>
       </c>
-      <c r="E467" s="10" t="s">
-        <v>493</v>
+      <c r="E467" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G467">
         <v>50.908999999999999</v>
@@ -29294,8 +29294,8 @@
       <c r="D468">
         <v>2010</v>
       </c>
-      <c r="E468" s="10" t="s">
-        <v>493</v>
+      <c r="E468" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G468">
         <v>52.254800000000003</v>
@@ -29347,8 +29347,8 @@
       <c r="D469">
         <v>2010</v>
       </c>
-      <c r="E469" s="10" t="s">
-        <v>493</v>
+      <c r="E469" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="G469">
         <v>51.493499999999997</v>
@@ -29400,8 +29400,8 @@
       <c r="D470">
         <v>2010</v>
       </c>
-      <c r="E470" s="10" t="s">
-        <v>493</v>
+      <c r="E470" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F470" t="s">
         <v>492</v>
@@ -29456,8 +29456,8 @@
       <c r="D471">
         <v>2010</v>
       </c>
-      <c r="E471" s="10" t="s">
-        <v>493</v>
+      <c r="E471" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F471" t="s">
         <v>491</v>
@@ -29512,8 +29512,8 @@
       <c r="D472">
         <v>2010</v>
       </c>
-      <c r="E472" s="10" t="s">
-        <v>493</v>
+      <c r="E472" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F472" t="s">
         <v>492</v>
@@ -29568,8 +29568,8 @@
       <c r="D473">
         <v>2010</v>
       </c>
-      <c r="E473" s="10" t="s">
-        <v>493</v>
+      <c r="E473" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F473" t="s">
         <v>492</v>
@@ -29624,8 +29624,8 @@
       <c r="D474">
         <v>2010</v>
       </c>
-      <c r="E474" s="10" t="s">
-        <v>493</v>
+      <c r="E474" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F474" t="s">
         <v>491</v>
@@ -29680,8 +29680,8 @@
       <c r="D475">
         <v>2010</v>
       </c>
-      <c r="E475" s="10" t="s">
-        <v>493</v>
+      <c r="E475" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F475" t="s">
         <v>491</v>
@@ -29736,8 +29736,8 @@
       <c r="D476">
         <v>2010</v>
       </c>
-      <c r="E476" s="10" t="s">
-        <v>493</v>
+      <c r="E476" s="9" t="s">
+        <v>540</v>
       </c>
       <c r="F476" t="s">
         <v>492</v>
